--- a/templates/song_template.xlsx
+++ b/templates/song_template.xlsx
@@ -97,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -132,6 +132,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -607,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T103"/>
+  <dimension ref="A1:T300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -761,7 +768,7 @@
           <t>제3회 동요샘 창작동요 발표회</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -776,22 +783,22 @@
           <t>가을</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="J2" s="12" t="inlineStr">
         <is>
           <t>학교생활, 몸놀이</t>
         </is>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="K2" s="12" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="L2" s="3" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
       </c>
-      <c r="M2" s="3" t="inlineStr">
+      <c r="M2" s="12" t="inlineStr">
         <is>
           <t>레~레</t>
         </is>
@@ -850,7 +857,7 @@
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr"/>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="12" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -865,14 +872,14 @@
           <t>사계절</t>
         </is>
       </c>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="J3" s="12" t="inlineStr">
         <is>
           <t>친구, 몸놀이</t>
         </is>
       </c>
-      <c r="K3" s="3" t="inlineStr"/>
-      <c r="L3" s="3" t="inlineStr"/>
-      <c r="M3" s="3" t="inlineStr"/>
+      <c r="K3" s="12" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr"/>
+      <c r="M3" s="12" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>둥글게 둥글게
@@ -901,13 +908,13 @@
       <c r="D4" s="4" t="n"/>
       <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
+      <c r="G4" s="13" t="n"/>
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
+      <c r="J4" s="13" t="n"/>
+      <c r="K4" s="13" t="n"/>
+      <c r="L4" s="13" t="n"/>
+      <c r="M4" s="13" t="n"/>
       <c r="N4" s="5" t="n"/>
       <c r="O4" s="5" t="n"/>
       <c r="P4" s="5" t="n"/>
@@ -923,13 +930,13 @@
       <c r="D5" s="4" t="n"/>
       <c r="E5" s="4" t="n"/>
       <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
+      <c r="G5" s="13" t="n"/>
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="4" t="n"/>
-      <c r="L5" s="4" t="n"/>
-      <c r="M5" s="4" t="n"/>
+      <c r="J5" s="13" t="n"/>
+      <c r="K5" s="13" t="n"/>
+      <c r="L5" s="13" t="n"/>
+      <c r="M5" s="13" t="n"/>
       <c r="N5" s="5" t="n"/>
       <c r="O5" s="5" t="n"/>
       <c r="P5" s="5" t="n"/>
@@ -945,13 +952,13 @@
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
       <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
+      <c r="G6" s="13" t="n"/>
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
+      <c r="J6" s="13" t="n"/>
+      <c r="K6" s="13" t="n"/>
+      <c r="L6" s="13" t="n"/>
+      <c r="M6" s="13" t="n"/>
       <c r="N6" s="5" t="n"/>
       <c r="O6" s="5" t="n"/>
       <c r="P6" s="5" t="n"/>
@@ -967,13 +974,13 @@
       <c r="D7" s="4" t="n"/>
       <c r="E7" s="4" t="n"/>
       <c r="F7" s="4" t="n"/>
-      <c r="G7" s="4" t="n"/>
+      <c r="G7" s="13" t="n"/>
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="4" t="n"/>
-      <c r="L7" s="4" t="n"/>
-      <c r="M7" s="4" t="n"/>
+      <c r="J7" s="13" t="n"/>
+      <c r="K7" s="13" t="n"/>
+      <c r="L7" s="13" t="n"/>
+      <c r="M7" s="13" t="n"/>
       <c r="N7" s="5" t="n"/>
       <c r="O7" s="5" t="n"/>
       <c r="P7" s="5" t="n"/>
@@ -989,13 +996,13 @@
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
-      <c r="G8" s="4" t="n"/>
+      <c r="G8" s="13" t="n"/>
       <c r="H8" s="4" t="n"/>
       <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
+      <c r="J8" s="13" t="n"/>
+      <c r="K8" s="13" t="n"/>
+      <c r="L8" s="13" t="n"/>
+      <c r="M8" s="13" t="n"/>
       <c r="N8" s="5" t="n"/>
       <c r="O8" s="5" t="n"/>
       <c r="P8" s="5" t="n"/>
@@ -1011,13 +1018,13 @@
       <c r="D9" s="4" t="n"/>
       <c r="E9" s="4" t="n"/>
       <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
+      <c r="G9" s="13" t="n"/>
       <c r="H9" s="4" t="n"/>
       <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
       <c r="N9" s="5" t="n"/>
       <c r="O9" s="5" t="n"/>
       <c r="P9" s="5" t="n"/>
@@ -1033,13 +1040,13 @@
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
+      <c r="G10" s="13" t="n"/>
       <c r="H10" s="4" t="n"/>
       <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
+      <c r="J10" s="13" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
       <c r="N10" s="5" t="n"/>
       <c r="O10" s="5" t="n"/>
       <c r="P10" s="5" t="n"/>
@@ -1055,13 +1062,13 @@
       <c r="D11" s="4" t="n"/>
       <c r="E11" s="4" t="n"/>
       <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
+      <c r="G11" s="13" t="n"/>
       <c r="H11" s="4" t="n"/>
       <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
+      <c r="J11" s="13" t="n"/>
+      <c r="K11" s="13" t="n"/>
+      <c r="L11" s="13" t="n"/>
+      <c r="M11" s="13" t="n"/>
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="n"/>
       <c r="P11" s="5" t="n"/>
@@ -1077,13 +1084,13 @@
       <c r="D12" s="4" t="n"/>
       <c r="E12" s="4" t="n"/>
       <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
+      <c r="G12" s="13" t="n"/>
       <c r="H12" s="4" t="n"/>
       <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
+      <c r="J12" s="13" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
       <c r="N12" s="5" t="n"/>
       <c r="O12" s="5" t="n"/>
       <c r="P12" s="5" t="n"/>
@@ -1099,13 +1106,13 @@
       <c r="D13" s="4" t="n"/>
       <c r="E13" s="4" t="n"/>
       <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+      <c r="G13" s="13" t="n"/>
       <c r="H13" s="4" t="n"/>
       <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
+      <c r="J13" s="13" t="n"/>
+      <c r="K13" s="13" t="n"/>
+      <c r="L13" s="13" t="n"/>
+      <c r="M13" s="13" t="n"/>
       <c r="N13" s="5" t="n"/>
       <c r="O13" s="5" t="n"/>
       <c r="P13" s="5" t="n"/>
@@ -1121,13 +1128,13 @@
       <c r="D14" s="4" t="n"/>
       <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
+      <c r="G14" s="13" t="n"/>
       <c r="H14" s="4" t="n"/>
       <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
+      <c r="J14" s="13" t="n"/>
+      <c r="K14" s="13" t="n"/>
+      <c r="L14" s="13" t="n"/>
+      <c r="M14" s="13" t="n"/>
       <c r="N14" s="5" t="n"/>
       <c r="O14" s="5" t="n"/>
       <c r="P14" s="5" t="n"/>
@@ -1143,13 +1150,13 @@
       <c r="D15" s="4" t="n"/>
       <c r="E15" s="4" t="n"/>
       <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
+      <c r="G15" s="13" t="n"/>
       <c r="H15" s="4" t="n"/>
       <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
+      <c r="J15" s="13" t="n"/>
+      <c r="K15" s="13" t="n"/>
+      <c r="L15" s="13" t="n"/>
+      <c r="M15" s="13" t="n"/>
       <c r="N15" s="5" t="n"/>
       <c r="O15" s="5" t="n"/>
       <c r="P15" s="5" t="n"/>
@@ -1165,13 +1172,13 @@
       <c r="D16" s="4" t="n"/>
       <c r="E16" s="4" t="n"/>
       <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
+      <c r="G16" s="13" t="n"/>
       <c r="H16" s="4" t="n"/>
       <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="13" t="n"/>
+      <c r="M16" s="13" t="n"/>
       <c r="N16" s="5" t="n"/>
       <c r="O16" s="5" t="n"/>
       <c r="P16" s="5" t="n"/>
@@ -1187,13 +1194,13 @@
       <c r="D17" s="4" t="n"/>
       <c r="E17" s="4" t="n"/>
       <c r="F17" s="4" t="n"/>
-      <c r="G17" s="4" t="n"/>
+      <c r="G17" s="13" t="n"/>
       <c r="H17" s="4" t="n"/>
       <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-      <c r="M17" s="4" t="n"/>
+      <c r="J17" s="13" t="n"/>
+      <c r="K17" s="13" t="n"/>
+      <c r="L17" s="13" t="n"/>
+      <c r="M17" s="13" t="n"/>
       <c r="N17" s="5" t="n"/>
       <c r="O17" s="5" t="n"/>
       <c r="P17" s="5" t="n"/>
@@ -1209,13 +1216,13 @@
       <c r="D18" s="4" t="n"/>
       <c r="E18" s="4" t="n"/>
       <c r="F18" s="4" t="n"/>
-      <c r="G18" s="4" t="n"/>
+      <c r="G18" s="13" t="n"/>
       <c r="H18" s="4" t="n"/>
       <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-      <c r="M18" s="4" t="n"/>
+      <c r="J18" s="13" t="n"/>
+      <c r="K18" s="13" t="n"/>
+      <c r="L18" s="13" t="n"/>
+      <c r="M18" s="13" t="n"/>
       <c r="N18" s="5" t="n"/>
       <c r="O18" s="5" t="n"/>
       <c r="P18" s="5" t="n"/>
@@ -1231,13 +1238,13 @@
       <c r="D19" s="4" t="n"/>
       <c r="E19" s="4" t="n"/>
       <c r="F19" s="4" t="n"/>
-      <c r="G19" s="4" t="n"/>
+      <c r="G19" s="13" t="n"/>
       <c r="H19" s="4" t="n"/>
       <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-      <c r="M19" s="4" t="n"/>
+      <c r="J19" s="13" t="n"/>
+      <c r="K19" s="13" t="n"/>
+      <c r="L19" s="13" t="n"/>
+      <c r="M19" s="13" t="n"/>
       <c r="N19" s="5" t="n"/>
       <c r="O19" s="5" t="n"/>
       <c r="P19" s="5" t="n"/>
@@ -1253,13 +1260,13 @@
       <c r="D20" s="4" t="n"/>
       <c r="E20" s="4" t="n"/>
       <c r="F20" s="4" t="n"/>
-      <c r="G20" s="4" t="n"/>
+      <c r="G20" s="13" t="n"/>
       <c r="H20" s="4" t="n"/>
       <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-      <c r="M20" s="4" t="n"/>
+      <c r="J20" s="13" t="n"/>
+      <c r="K20" s="13" t="n"/>
+      <c r="L20" s="13" t="n"/>
+      <c r="M20" s="13" t="n"/>
       <c r="N20" s="5" t="n"/>
       <c r="O20" s="5" t="n"/>
       <c r="P20" s="5" t="n"/>
@@ -1275,13 +1282,13 @@
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
-      <c r="G21" s="4" t="n"/>
+      <c r="G21" s="13" t="n"/>
       <c r="H21" s="4" t="n"/>
       <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-      <c r="M21" s="4" t="n"/>
+      <c r="J21" s="13" t="n"/>
+      <c r="K21" s="13" t="n"/>
+      <c r="L21" s="13" t="n"/>
+      <c r="M21" s="13" t="n"/>
       <c r="N21" s="5" t="n"/>
       <c r="O21" s="5" t="n"/>
       <c r="P21" s="5" t="n"/>
@@ -1297,13 +1304,13 @@
       <c r="D22" s="4" t="n"/>
       <c r="E22" s="4" t="n"/>
       <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
+      <c r="G22" s="13" t="n"/>
       <c r="H22" s="4" t="n"/>
       <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
+      <c r="J22" s="13" t="n"/>
+      <c r="K22" s="13" t="n"/>
+      <c r="L22" s="13" t="n"/>
+      <c r="M22" s="13" t="n"/>
       <c r="N22" s="5" t="n"/>
       <c r="O22" s="5" t="n"/>
       <c r="P22" s="5" t="n"/>
@@ -1319,13 +1326,13 @@
       <c r="D23" s="4" t="n"/>
       <c r="E23" s="4" t="n"/>
       <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
+      <c r="G23" s="13" t="n"/>
       <c r="H23" s="4" t="n"/>
       <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
+      <c r="J23" s="13" t="n"/>
+      <c r="K23" s="13" t="n"/>
+      <c r="L23" s="13" t="n"/>
+      <c r="M23" s="13" t="n"/>
       <c r="N23" s="5" t="n"/>
       <c r="O23" s="5" t="n"/>
       <c r="P23" s="5" t="n"/>
@@ -1341,13 +1348,13 @@
       <c r="D24" s="4" t="n"/>
       <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
+      <c r="G24" s="13" t="n"/>
       <c r="H24" s="4" t="n"/>
       <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
+      <c r="J24" s="13" t="n"/>
+      <c r="K24" s="13" t="n"/>
+      <c r="L24" s="13" t="n"/>
+      <c r="M24" s="13" t="n"/>
       <c r="N24" s="5" t="n"/>
       <c r="O24" s="5" t="n"/>
       <c r="P24" s="5" t="n"/>
@@ -1363,13 +1370,13 @@
       <c r="D25" s="4" t="n"/>
       <c r="E25" s="4" t="n"/>
       <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
+      <c r="G25" s="13" t="n"/>
       <c r="H25" s="4" t="n"/>
       <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
+      <c r="J25" s="13" t="n"/>
+      <c r="K25" s="13" t="n"/>
+      <c r="L25" s="13" t="n"/>
+      <c r="M25" s="13" t="n"/>
       <c r="N25" s="5" t="n"/>
       <c r="O25" s="5" t="n"/>
       <c r="P25" s="5" t="n"/>
@@ -1385,13 +1392,13 @@
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
-      <c r="G26" s="4" t="n"/>
+      <c r="G26" s="13" t="n"/>
       <c r="H26" s="4" t="n"/>
       <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-      <c r="M26" s="4" t="n"/>
+      <c r="J26" s="13" t="n"/>
+      <c r="K26" s="13" t="n"/>
+      <c r="L26" s="13" t="n"/>
+      <c r="M26" s="13" t="n"/>
       <c r="N26" s="5" t="n"/>
       <c r="O26" s="5" t="n"/>
       <c r="P26" s="5" t="n"/>
@@ -1407,13 +1414,13 @@
       <c r="D27" s="4" t="n"/>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
+      <c r="G27" s="13" t="n"/>
       <c r="H27" s="4" t="n"/>
       <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
+      <c r="J27" s="13" t="n"/>
+      <c r="K27" s="13" t="n"/>
+      <c r="L27" s="13" t="n"/>
+      <c r="M27" s="13" t="n"/>
       <c r="N27" s="5" t="n"/>
       <c r="O27" s="5" t="n"/>
       <c r="P27" s="5" t="n"/>
@@ -1429,13 +1436,13 @@
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
+      <c r="G28" s="13" t="n"/>
       <c r="H28" s="4" t="n"/>
       <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
+      <c r="J28" s="13" t="n"/>
+      <c r="K28" s="13" t="n"/>
+      <c r="L28" s="13" t="n"/>
+      <c r="M28" s="13" t="n"/>
       <c r="N28" s="5" t="n"/>
       <c r="O28" s="5" t="n"/>
       <c r="P28" s="5" t="n"/>
@@ -1451,13 +1458,13 @@
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
+      <c r="G29" s="13" t="n"/>
       <c r="H29" s="4" t="n"/>
       <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-      <c r="M29" s="4" t="n"/>
+      <c r="J29" s="13" t="n"/>
+      <c r="K29" s="13" t="n"/>
+      <c r="L29" s="13" t="n"/>
+      <c r="M29" s="13" t="n"/>
       <c r="N29" s="5" t="n"/>
       <c r="O29" s="5" t="n"/>
       <c r="P29" s="5" t="n"/>
@@ -1473,13 +1480,13 @@
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="n"/>
-      <c r="G30" s="4" t="n"/>
+      <c r="G30" s="13" t="n"/>
       <c r="H30" s="4" t="n"/>
       <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-      <c r="M30" s="4" t="n"/>
+      <c r="J30" s="13" t="n"/>
+      <c r="K30" s="13" t="n"/>
+      <c r="L30" s="13" t="n"/>
+      <c r="M30" s="13" t="n"/>
       <c r="N30" s="5" t="n"/>
       <c r="O30" s="5" t="n"/>
       <c r="P30" s="5" t="n"/>
@@ -1495,13 +1502,13 @@
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="n"/>
-      <c r="G31" s="4" t="n"/>
+      <c r="G31" s="13" t="n"/>
       <c r="H31" s="4" t="n"/>
       <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-      <c r="M31" s="4" t="n"/>
+      <c r="J31" s="13" t="n"/>
+      <c r="K31" s="13" t="n"/>
+      <c r="L31" s="13" t="n"/>
+      <c r="M31" s="13" t="n"/>
       <c r="N31" s="5" t="n"/>
       <c r="O31" s="5" t="n"/>
       <c r="P31" s="5" t="n"/>
@@ -1517,13 +1524,13 @@
       <c r="D32" s="4" t="n"/>
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="n"/>
-      <c r="G32" s="4" t="n"/>
+      <c r="G32" s="13" t="n"/>
       <c r="H32" s="4" t="n"/>
       <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-      <c r="M32" s="4" t="n"/>
+      <c r="J32" s="13" t="n"/>
+      <c r="K32" s="13" t="n"/>
+      <c r="L32" s="13" t="n"/>
+      <c r="M32" s="13" t="n"/>
       <c r="N32" s="5" t="n"/>
       <c r="O32" s="5" t="n"/>
       <c r="P32" s="5" t="n"/>
@@ -1539,13 +1546,13 @@
       <c r="D33" s="4" t="n"/>
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="n"/>
-      <c r="G33" s="4" t="n"/>
+      <c r="G33" s="13" t="n"/>
       <c r="H33" s="4" t="n"/>
       <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-      <c r="M33" s="4" t="n"/>
+      <c r="J33" s="13" t="n"/>
+      <c r="K33" s="13" t="n"/>
+      <c r="L33" s="13" t="n"/>
+      <c r="M33" s="13" t="n"/>
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="n"/>
       <c r="P33" s="5" t="n"/>
@@ -1561,13 +1568,13 @@
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
       <c r="F34" s="4" t="n"/>
-      <c r="G34" s="4" t="n"/>
+      <c r="G34" s="13" t="n"/>
       <c r="H34" s="4" t="n"/>
       <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
+      <c r="J34" s="13" t="n"/>
+      <c r="K34" s="13" t="n"/>
+      <c r="L34" s="13" t="n"/>
+      <c r="M34" s="13" t="n"/>
       <c r="N34" s="5" t="n"/>
       <c r="O34" s="5" t="n"/>
       <c r="P34" s="5" t="n"/>
@@ -1583,13 +1590,13 @@
       <c r="D35" s="4" t="n"/>
       <c r="E35" s="4" t="n"/>
       <c r="F35" s="4" t="n"/>
-      <c r="G35" s="4" t="n"/>
+      <c r="G35" s="13" t="n"/>
       <c r="H35" s="4" t="n"/>
       <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
+      <c r="J35" s="13" t="n"/>
+      <c r="K35" s="13" t="n"/>
+      <c r="L35" s="13" t="n"/>
+      <c r="M35" s="13" t="n"/>
       <c r="N35" s="5" t="n"/>
       <c r="O35" s="5" t="n"/>
       <c r="P35" s="5" t="n"/>
@@ -1605,13 +1612,13 @@
       <c r="D36" s="4" t="n"/>
       <c r="E36" s="4" t="n"/>
       <c r="F36" s="4" t="n"/>
-      <c r="G36" s="4" t="n"/>
+      <c r="G36" s="13" t="n"/>
       <c r="H36" s="4" t="n"/>
       <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
+      <c r="J36" s="13" t="n"/>
+      <c r="K36" s="13" t="n"/>
+      <c r="L36" s="13" t="n"/>
+      <c r="M36" s="13" t="n"/>
       <c r="N36" s="5" t="n"/>
       <c r="O36" s="5" t="n"/>
       <c r="P36" s="5" t="n"/>
@@ -1627,13 +1634,13 @@
       <c r="D37" s="4" t="n"/>
       <c r="E37" s="4" t="n"/>
       <c r="F37" s="4" t="n"/>
-      <c r="G37" s="4" t="n"/>
+      <c r="G37" s="13" t="n"/>
       <c r="H37" s="4" t="n"/>
       <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-      <c r="M37" s="4" t="n"/>
+      <c r="J37" s="13" t="n"/>
+      <c r="K37" s="13" t="n"/>
+      <c r="L37" s="13" t="n"/>
+      <c r="M37" s="13" t="n"/>
       <c r="N37" s="5" t="n"/>
       <c r="O37" s="5" t="n"/>
       <c r="P37" s="5" t="n"/>
@@ -1649,13 +1656,13 @@
       <c r="D38" s="4" t="n"/>
       <c r="E38" s="4" t="n"/>
       <c r="F38" s="4" t="n"/>
-      <c r="G38" s="4" t="n"/>
+      <c r="G38" s="13" t="n"/>
       <c r="H38" s="4" t="n"/>
       <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-      <c r="M38" s="4" t="n"/>
+      <c r="J38" s="13" t="n"/>
+      <c r="K38" s="13" t="n"/>
+      <c r="L38" s="13" t="n"/>
+      <c r="M38" s="13" t="n"/>
       <c r="N38" s="5" t="n"/>
       <c r="O38" s="5" t="n"/>
       <c r="P38" s="5" t="n"/>
@@ -1671,13 +1678,13 @@
       <c r="D39" s="4" t="n"/>
       <c r="E39" s="4" t="n"/>
       <c r="F39" s="4" t="n"/>
-      <c r="G39" s="4" t="n"/>
+      <c r="G39" s="13" t="n"/>
       <c r="H39" s="4" t="n"/>
       <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-      <c r="M39" s="4" t="n"/>
+      <c r="J39" s="13" t="n"/>
+      <c r="K39" s="13" t="n"/>
+      <c r="L39" s="13" t="n"/>
+      <c r="M39" s="13" t="n"/>
       <c r="N39" s="5" t="n"/>
       <c r="O39" s="5" t="n"/>
       <c r="P39" s="5" t="n"/>
@@ -1693,13 +1700,13 @@
       <c r="D40" s="4" t="n"/>
       <c r="E40" s="4" t="n"/>
       <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
+      <c r="G40" s="13" t="n"/>
       <c r="H40" s="4" t="n"/>
       <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-      <c r="M40" s="4" t="n"/>
+      <c r="J40" s="13" t="n"/>
+      <c r="K40" s="13" t="n"/>
+      <c r="L40" s="13" t="n"/>
+      <c r="M40" s="13" t="n"/>
       <c r="N40" s="5" t="n"/>
       <c r="O40" s="5" t="n"/>
       <c r="P40" s="5" t="n"/>
@@ -1715,13 +1722,13 @@
       <c r="D41" s="4" t="n"/>
       <c r="E41" s="4" t="n"/>
       <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
+      <c r="G41" s="13" t="n"/>
       <c r="H41" s="4" t="n"/>
       <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-      <c r="M41" s="4" t="n"/>
+      <c r="J41" s="13" t="n"/>
+      <c r="K41" s="13" t="n"/>
+      <c r="L41" s="13" t="n"/>
+      <c r="M41" s="13" t="n"/>
       <c r="N41" s="5" t="n"/>
       <c r="O41" s="5" t="n"/>
       <c r="P41" s="5" t="n"/>
@@ -1737,13 +1744,13 @@
       <c r="D42" s="4" t="n"/>
       <c r="E42" s="4" t="n"/>
       <c r="F42" s="4" t="n"/>
-      <c r="G42" s="4" t="n"/>
+      <c r="G42" s="13" t="n"/>
       <c r="H42" s="4" t="n"/>
       <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
-      <c r="M42" s="4" t="n"/>
+      <c r="J42" s="13" t="n"/>
+      <c r="K42" s="13" t="n"/>
+      <c r="L42" s="13" t="n"/>
+      <c r="M42" s="13" t="n"/>
       <c r="N42" s="5" t="n"/>
       <c r="O42" s="5" t="n"/>
       <c r="P42" s="5" t="n"/>
@@ -1759,13 +1766,13 @@
       <c r="D43" s="4" t="n"/>
       <c r="E43" s="4" t="n"/>
       <c r="F43" s="4" t="n"/>
-      <c r="G43" s="4" t="n"/>
+      <c r="G43" s="13" t="n"/>
       <c r="H43" s="4" t="n"/>
       <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-      <c r="M43" s="4" t="n"/>
+      <c r="J43" s="13" t="n"/>
+      <c r="K43" s="13" t="n"/>
+      <c r="L43" s="13" t="n"/>
+      <c r="M43" s="13" t="n"/>
       <c r="N43" s="5" t="n"/>
       <c r="O43" s="5" t="n"/>
       <c r="P43" s="5" t="n"/>
@@ -1781,13 +1788,13 @@
       <c r="D44" s="4" t="n"/>
       <c r="E44" s="4" t="n"/>
       <c r="F44" s="4" t="n"/>
-      <c r="G44" s="4" t="n"/>
+      <c r="G44" s="13" t="n"/>
       <c r="H44" s="4" t="n"/>
       <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-      <c r="M44" s="4" t="n"/>
+      <c r="J44" s="13" t="n"/>
+      <c r="K44" s="13" t="n"/>
+      <c r="L44" s="13" t="n"/>
+      <c r="M44" s="13" t="n"/>
       <c r="N44" s="5" t="n"/>
       <c r="O44" s="5" t="n"/>
       <c r="P44" s="5" t="n"/>
@@ -1803,13 +1810,13 @@
       <c r="D45" s="4" t="n"/>
       <c r="E45" s="4" t="n"/>
       <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
+      <c r="G45" s="13" t="n"/>
       <c r="H45" s="4" t="n"/>
       <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-      <c r="M45" s="4" t="n"/>
+      <c r="J45" s="13" t="n"/>
+      <c r="K45" s="13" t="n"/>
+      <c r="L45" s="13" t="n"/>
+      <c r="M45" s="13" t="n"/>
       <c r="N45" s="5" t="n"/>
       <c r="O45" s="5" t="n"/>
       <c r="P45" s="5" t="n"/>
@@ -1825,13 +1832,13 @@
       <c r="D46" s="4" t="n"/>
       <c r="E46" s="4" t="n"/>
       <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
+      <c r="G46" s="13" t="n"/>
       <c r="H46" s="4" t="n"/>
       <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-      <c r="M46" s="4" t="n"/>
+      <c r="J46" s="13" t="n"/>
+      <c r="K46" s="13" t="n"/>
+      <c r="L46" s="13" t="n"/>
+      <c r="M46" s="13" t="n"/>
       <c r="N46" s="5" t="n"/>
       <c r="O46" s="5" t="n"/>
       <c r="P46" s="5" t="n"/>
@@ -1847,13 +1854,13 @@
       <c r="D47" s="4" t="n"/>
       <c r="E47" s="4" t="n"/>
       <c r="F47" s="4" t="n"/>
-      <c r="G47" s="4" t="n"/>
+      <c r="G47" s="13" t="n"/>
       <c r="H47" s="4" t="n"/>
       <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-      <c r="M47" s="4" t="n"/>
+      <c r="J47" s="13" t="n"/>
+      <c r="K47" s="13" t="n"/>
+      <c r="L47" s="13" t="n"/>
+      <c r="M47" s="13" t="n"/>
       <c r="N47" s="5" t="n"/>
       <c r="O47" s="5" t="n"/>
       <c r="P47" s="5" t="n"/>
@@ -1869,13 +1876,13 @@
       <c r="D48" s="4" t="n"/>
       <c r="E48" s="4" t="n"/>
       <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
+      <c r="G48" s="13" t="n"/>
       <c r="H48" s="4" t="n"/>
       <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-      <c r="M48" s="4" t="n"/>
+      <c r="J48" s="13" t="n"/>
+      <c r="K48" s="13" t="n"/>
+      <c r="L48" s="13" t="n"/>
+      <c r="M48" s="13" t="n"/>
       <c r="N48" s="5" t="n"/>
       <c r="O48" s="5" t="n"/>
       <c r="P48" s="5" t="n"/>
@@ -1891,13 +1898,13 @@
       <c r="D49" s="4" t="n"/>
       <c r="E49" s="4" t="n"/>
       <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
+      <c r="G49" s="13" t="n"/>
       <c r="H49" s="4" t="n"/>
       <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="4" t="n"/>
-      <c r="M49" s="4" t="n"/>
+      <c r="J49" s="13" t="n"/>
+      <c r="K49" s="13" t="n"/>
+      <c r="L49" s="13" t="n"/>
+      <c r="M49" s="13" t="n"/>
       <c r="N49" s="5" t="n"/>
       <c r="O49" s="5" t="n"/>
       <c r="P49" s="5" t="n"/>
@@ -1913,13 +1920,13 @@
       <c r="D50" s="4" t="n"/>
       <c r="E50" s="4" t="n"/>
       <c r="F50" s="4" t="n"/>
-      <c r="G50" s="4" t="n"/>
+      <c r="G50" s="13" t="n"/>
       <c r="H50" s="4" t="n"/>
       <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
-      <c r="M50" s="4" t="n"/>
+      <c r="J50" s="13" t="n"/>
+      <c r="K50" s="13" t="n"/>
+      <c r="L50" s="13" t="n"/>
+      <c r="M50" s="13" t="n"/>
       <c r="N50" s="5" t="n"/>
       <c r="O50" s="5" t="n"/>
       <c r="P50" s="5" t="n"/>
@@ -1935,13 +1942,13 @@
       <c r="D51" s="4" t="n"/>
       <c r="E51" s="4" t="n"/>
       <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
+      <c r="G51" s="13" t="n"/>
       <c r="H51" s="4" t="n"/>
       <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
+      <c r="J51" s="13" t="n"/>
+      <c r="K51" s="13" t="n"/>
+      <c r="L51" s="13" t="n"/>
+      <c r="M51" s="13" t="n"/>
       <c r="N51" s="5" t="n"/>
       <c r="O51" s="5" t="n"/>
       <c r="P51" s="5" t="n"/>
@@ -1957,13 +1964,13 @@
       <c r="D52" s="4" t="n"/>
       <c r="E52" s="4" t="n"/>
       <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
+      <c r="G52" s="13" t="n"/>
       <c r="H52" s="4" t="n"/>
       <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
+      <c r="J52" s="13" t="n"/>
+      <c r="K52" s="13" t="n"/>
+      <c r="L52" s="13" t="n"/>
+      <c r="M52" s="13" t="n"/>
       <c r="N52" s="5" t="n"/>
       <c r="O52" s="5" t="n"/>
       <c r="P52" s="5" t="n"/>
@@ -1979,13 +1986,13 @@
       <c r="D53" s="4" t="n"/>
       <c r="E53" s="4" t="n"/>
       <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
+      <c r="G53" s="13" t="n"/>
       <c r="H53" s="4" t="n"/>
       <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-      <c r="M53" s="4" t="n"/>
+      <c r="J53" s="13" t="n"/>
+      <c r="K53" s="13" t="n"/>
+      <c r="L53" s="13" t="n"/>
+      <c r="M53" s="13" t="n"/>
       <c r="N53" s="5" t="n"/>
       <c r="O53" s="5" t="n"/>
       <c r="P53" s="5" t="n"/>
@@ -2001,13 +2008,13 @@
       <c r="D54" s="4" t="n"/>
       <c r="E54" s="4" t="n"/>
       <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
+      <c r="G54" s="13" t="n"/>
       <c r="H54" s="4" t="n"/>
       <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-      <c r="M54" s="4" t="n"/>
+      <c r="J54" s="13" t="n"/>
+      <c r="K54" s="13" t="n"/>
+      <c r="L54" s="13" t="n"/>
+      <c r="M54" s="13" t="n"/>
       <c r="N54" s="5" t="n"/>
       <c r="O54" s="5" t="n"/>
       <c r="P54" s="5" t="n"/>
@@ -2023,13 +2030,13 @@
       <c r="D55" s="4" t="n"/>
       <c r="E55" s="4" t="n"/>
       <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
+      <c r="G55" s="13" t="n"/>
       <c r="H55" s="4" t="n"/>
       <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
+      <c r="J55" s="13" t="n"/>
+      <c r="K55" s="13" t="n"/>
+      <c r="L55" s="13" t="n"/>
+      <c r="M55" s="13" t="n"/>
       <c r="N55" s="5" t="n"/>
       <c r="O55" s="5" t="n"/>
       <c r="P55" s="5" t="n"/>
@@ -2045,13 +2052,13 @@
       <c r="D56" s="4" t="n"/>
       <c r="E56" s="4" t="n"/>
       <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
+      <c r="G56" s="13" t="n"/>
       <c r="H56" s="4" t="n"/>
       <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n"/>
-      <c r="M56" s="4" t="n"/>
+      <c r="J56" s="13" t="n"/>
+      <c r="K56" s="13" t="n"/>
+      <c r="L56" s="13" t="n"/>
+      <c r="M56" s="13" t="n"/>
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5" t="n"/>
       <c r="P56" s="5" t="n"/>
@@ -2067,13 +2074,13 @@
       <c r="D57" s="4" t="n"/>
       <c r="E57" s="4" t="n"/>
       <c r="F57" s="4" t="n"/>
-      <c r="G57" s="4" t="n"/>
+      <c r="G57" s="13" t="n"/>
       <c r="H57" s="4" t="n"/>
       <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-      <c r="M57" s="4" t="n"/>
+      <c r="J57" s="13" t="n"/>
+      <c r="K57" s="13" t="n"/>
+      <c r="L57" s="13" t="n"/>
+      <c r="M57" s="13" t="n"/>
       <c r="N57" s="5" t="n"/>
       <c r="O57" s="5" t="n"/>
       <c r="P57" s="5" t="n"/>
@@ -2089,13 +2096,13 @@
       <c r="D58" s="4" t="n"/>
       <c r="E58" s="4" t="n"/>
       <c r="F58" s="4" t="n"/>
-      <c r="G58" s="4" t="n"/>
+      <c r="G58" s="13" t="n"/>
       <c r="H58" s="4" t="n"/>
       <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
-      <c r="M58" s="4" t="n"/>
+      <c r="J58" s="13" t="n"/>
+      <c r="K58" s="13" t="n"/>
+      <c r="L58" s="13" t="n"/>
+      <c r="M58" s="13" t="n"/>
       <c r="N58" s="5" t="n"/>
       <c r="O58" s="5" t="n"/>
       <c r="P58" s="5" t="n"/>
@@ -2111,13 +2118,13 @@
       <c r="D59" s="4" t="n"/>
       <c r="E59" s="4" t="n"/>
       <c r="F59" s="4" t="n"/>
-      <c r="G59" s="4" t="n"/>
+      <c r="G59" s="13" t="n"/>
       <c r="H59" s="4" t="n"/>
       <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n"/>
-      <c r="M59" s="4" t="n"/>
+      <c r="J59" s="13" t="n"/>
+      <c r="K59" s="13" t="n"/>
+      <c r="L59" s="13" t="n"/>
+      <c r="M59" s="13" t="n"/>
       <c r="N59" s="5" t="n"/>
       <c r="O59" s="5" t="n"/>
       <c r="P59" s="5" t="n"/>
@@ -2133,13 +2140,13 @@
       <c r="D60" s="4" t="n"/>
       <c r="E60" s="4" t="n"/>
       <c r="F60" s="4" t="n"/>
-      <c r="G60" s="4" t="n"/>
+      <c r="G60" s="13" t="n"/>
       <c r="H60" s="4" t="n"/>
       <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-      <c r="M60" s="4" t="n"/>
+      <c r="J60" s="13" t="n"/>
+      <c r="K60" s="13" t="n"/>
+      <c r="L60" s="13" t="n"/>
+      <c r="M60" s="13" t="n"/>
       <c r="N60" s="5" t="n"/>
       <c r="O60" s="5" t="n"/>
       <c r="P60" s="5" t="n"/>
@@ -2155,13 +2162,13 @@
       <c r="D61" s="4" t="n"/>
       <c r="E61" s="4" t="n"/>
       <c r="F61" s="4" t="n"/>
-      <c r="G61" s="4" t="n"/>
+      <c r="G61" s="13" t="n"/>
       <c r="H61" s="4" t="n"/>
       <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-      <c r="M61" s="4" t="n"/>
+      <c r="J61" s="13" t="n"/>
+      <c r="K61" s="13" t="n"/>
+      <c r="L61" s="13" t="n"/>
+      <c r="M61" s="13" t="n"/>
       <c r="N61" s="5" t="n"/>
       <c r="O61" s="5" t="n"/>
       <c r="P61" s="5" t="n"/>
@@ -2177,13 +2184,13 @@
       <c r="D62" s="4" t="n"/>
       <c r="E62" s="4" t="n"/>
       <c r="F62" s="4" t="n"/>
-      <c r="G62" s="4" t="n"/>
+      <c r="G62" s="13" t="n"/>
       <c r="H62" s="4" t="n"/>
       <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
-      <c r="M62" s="4" t="n"/>
+      <c r="J62" s="13" t="n"/>
+      <c r="K62" s="13" t="n"/>
+      <c r="L62" s="13" t="n"/>
+      <c r="M62" s="13" t="n"/>
       <c r="N62" s="5" t="n"/>
       <c r="O62" s="5" t="n"/>
       <c r="P62" s="5" t="n"/>
@@ -2199,13 +2206,13 @@
       <c r="D63" s="4" t="n"/>
       <c r="E63" s="4" t="n"/>
       <c r="F63" s="4" t="n"/>
-      <c r="G63" s="4" t="n"/>
+      <c r="G63" s="13" t="n"/>
       <c r="H63" s="4" t="n"/>
       <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n"/>
-      <c r="M63" s="4" t="n"/>
+      <c r="J63" s="13" t="n"/>
+      <c r="K63" s="13" t="n"/>
+      <c r="L63" s="13" t="n"/>
+      <c r="M63" s="13" t="n"/>
       <c r="N63" s="5" t="n"/>
       <c r="O63" s="5" t="n"/>
       <c r="P63" s="5" t="n"/>
@@ -2221,13 +2228,13 @@
       <c r="D64" s="4" t="n"/>
       <c r="E64" s="4" t="n"/>
       <c r="F64" s="4" t="n"/>
-      <c r="G64" s="4" t="n"/>
+      <c r="G64" s="13" t="n"/>
       <c r="H64" s="4" t="n"/>
       <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-      <c r="M64" s="4" t="n"/>
+      <c r="J64" s="13" t="n"/>
+      <c r="K64" s="13" t="n"/>
+      <c r="L64" s="13" t="n"/>
+      <c r="M64" s="13" t="n"/>
       <c r="N64" s="5" t="n"/>
       <c r="O64" s="5" t="n"/>
       <c r="P64" s="5" t="n"/>
@@ -2243,13 +2250,13 @@
       <c r="D65" s="4" t="n"/>
       <c r="E65" s="4" t="n"/>
       <c r="F65" s="4" t="n"/>
-      <c r="G65" s="4" t="n"/>
+      <c r="G65" s="13" t="n"/>
       <c r="H65" s="4" t="n"/>
       <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-      <c r="M65" s="4" t="n"/>
+      <c r="J65" s="13" t="n"/>
+      <c r="K65" s="13" t="n"/>
+      <c r="L65" s="13" t="n"/>
+      <c r="M65" s="13" t="n"/>
       <c r="N65" s="5" t="n"/>
       <c r="O65" s="5" t="n"/>
       <c r="P65" s="5" t="n"/>
@@ -2265,13 +2272,13 @@
       <c r="D66" s="4" t="n"/>
       <c r="E66" s="4" t="n"/>
       <c r="F66" s="4" t="n"/>
-      <c r="G66" s="4" t="n"/>
+      <c r="G66" s="13" t="n"/>
       <c r="H66" s="4" t="n"/>
       <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
-      <c r="M66" s="4" t="n"/>
+      <c r="J66" s="13" t="n"/>
+      <c r="K66" s="13" t="n"/>
+      <c r="L66" s="13" t="n"/>
+      <c r="M66" s="13" t="n"/>
       <c r="N66" s="5" t="n"/>
       <c r="O66" s="5" t="n"/>
       <c r="P66" s="5" t="n"/>
@@ -2287,13 +2294,13 @@
       <c r="D67" s="4" t="n"/>
       <c r="E67" s="4" t="n"/>
       <c r="F67" s="4" t="n"/>
-      <c r="G67" s="4" t="n"/>
+      <c r="G67" s="13" t="n"/>
       <c r="H67" s="4" t="n"/>
       <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-      <c r="M67" s="4" t="n"/>
+      <c r="J67" s="13" t="n"/>
+      <c r="K67" s="13" t="n"/>
+      <c r="L67" s="13" t="n"/>
+      <c r="M67" s="13" t="n"/>
       <c r="N67" s="5" t="n"/>
       <c r="O67" s="5" t="n"/>
       <c r="P67" s="5" t="n"/>
@@ -2309,13 +2316,13 @@
       <c r="D68" s="4" t="n"/>
       <c r="E68" s="4" t="n"/>
       <c r="F68" s="4" t="n"/>
-      <c r="G68" s="4" t="n"/>
+      <c r="G68" s="13" t="n"/>
       <c r="H68" s="4" t="n"/>
       <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-      <c r="M68" s="4" t="n"/>
+      <c r="J68" s="13" t="n"/>
+      <c r="K68" s="13" t="n"/>
+      <c r="L68" s="13" t="n"/>
+      <c r="M68" s="13" t="n"/>
       <c r="N68" s="5" t="n"/>
       <c r="O68" s="5" t="n"/>
       <c r="P68" s="5" t="n"/>
@@ -2331,13 +2338,13 @@
       <c r="D69" s="4" t="n"/>
       <c r="E69" s="4" t="n"/>
       <c r="F69" s="4" t="n"/>
-      <c r="G69" s="4" t="n"/>
+      <c r="G69" s="13" t="n"/>
       <c r="H69" s="4" t="n"/>
       <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-      <c r="M69" s="4" t="n"/>
+      <c r="J69" s="13" t="n"/>
+      <c r="K69" s="13" t="n"/>
+      <c r="L69" s="13" t="n"/>
+      <c r="M69" s="13" t="n"/>
       <c r="N69" s="5" t="n"/>
       <c r="O69" s="5" t="n"/>
       <c r="P69" s="5" t="n"/>
@@ -2353,13 +2360,13 @@
       <c r="D70" s="4" t="n"/>
       <c r="E70" s="4" t="n"/>
       <c r="F70" s="4" t="n"/>
-      <c r="G70" s="4" t="n"/>
+      <c r="G70" s="13" t="n"/>
       <c r="H70" s="4" t="n"/>
       <c r="I70" s="4" t="n"/>
-      <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
-      <c r="M70" s="4" t="n"/>
+      <c r="J70" s="13" t="n"/>
+      <c r="K70" s="13" t="n"/>
+      <c r="L70" s="13" t="n"/>
+      <c r="M70" s="13" t="n"/>
       <c r="N70" s="5" t="n"/>
       <c r="O70" s="5" t="n"/>
       <c r="P70" s="5" t="n"/>
@@ -2375,13 +2382,13 @@
       <c r="D71" s="4" t="n"/>
       <c r="E71" s="4" t="n"/>
       <c r="F71" s="4" t="n"/>
-      <c r="G71" s="4" t="n"/>
+      <c r="G71" s="13" t="n"/>
       <c r="H71" s="4" t="n"/>
       <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
-      <c r="M71" s="4" t="n"/>
+      <c r="J71" s="13" t="n"/>
+      <c r="K71" s="13" t="n"/>
+      <c r="L71" s="13" t="n"/>
+      <c r="M71" s="13" t="n"/>
       <c r="N71" s="5" t="n"/>
       <c r="O71" s="5" t="n"/>
       <c r="P71" s="5" t="n"/>
@@ -2397,13 +2404,13 @@
       <c r="D72" s="4" t="n"/>
       <c r="E72" s="4" t="n"/>
       <c r="F72" s="4" t="n"/>
-      <c r="G72" s="4" t="n"/>
+      <c r="G72" s="13" t="n"/>
       <c r="H72" s="4" t="n"/>
       <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
-      <c r="M72" s="4" t="n"/>
+      <c r="J72" s="13" t="n"/>
+      <c r="K72" s="13" t="n"/>
+      <c r="L72" s="13" t="n"/>
+      <c r="M72" s="13" t="n"/>
       <c r="N72" s="5" t="n"/>
       <c r="O72" s="5" t="n"/>
       <c r="P72" s="5" t="n"/>
@@ -2419,13 +2426,13 @@
       <c r="D73" s="4" t="n"/>
       <c r="E73" s="4" t="n"/>
       <c r="F73" s="4" t="n"/>
-      <c r="G73" s="4" t="n"/>
+      <c r="G73" s="13" t="n"/>
       <c r="H73" s="4" t="n"/>
       <c r="I73" s="4" t="n"/>
-      <c r="J73" s="4" t="n"/>
-      <c r="K73" s="4" t="n"/>
-      <c r="L73" s="4" t="n"/>
-      <c r="M73" s="4" t="n"/>
+      <c r="J73" s="13" t="n"/>
+      <c r="K73" s="13" t="n"/>
+      <c r="L73" s="13" t="n"/>
+      <c r="M73" s="13" t="n"/>
       <c r="N73" s="5" t="n"/>
       <c r="O73" s="5" t="n"/>
       <c r="P73" s="5" t="n"/>
@@ -2441,13 +2448,13 @@
       <c r="D74" s="4" t="n"/>
       <c r="E74" s="4" t="n"/>
       <c r="F74" s="4" t="n"/>
-      <c r="G74" s="4" t="n"/>
+      <c r="G74" s="13" t="n"/>
       <c r="H74" s="4" t="n"/>
       <c r="I74" s="4" t="n"/>
-      <c r="J74" s="4" t="n"/>
-      <c r="K74" s="4" t="n"/>
-      <c r="L74" s="4" t="n"/>
-      <c r="M74" s="4" t="n"/>
+      <c r="J74" s="13" t="n"/>
+      <c r="K74" s="13" t="n"/>
+      <c r="L74" s="13" t="n"/>
+      <c r="M74" s="13" t="n"/>
       <c r="N74" s="5" t="n"/>
       <c r="O74" s="5" t="n"/>
       <c r="P74" s="5" t="n"/>
@@ -2463,13 +2470,13 @@
       <c r="D75" s="4" t="n"/>
       <c r="E75" s="4" t="n"/>
       <c r="F75" s="4" t="n"/>
-      <c r="G75" s="4" t="n"/>
+      <c r="G75" s="13" t="n"/>
       <c r="H75" s="4" t="n"/>
       <c r="I75" s="4" t="n"/>
-      <c r="J75" s="4" t="n"/>
-      <c r="K75" s="4" t="n"/>
-      <c r="L75" s="4" t="n"/>
-      <c r="M75" s="4" t="n"/>
+      <c r="J75" s="13" t="n"/>
+      <c r="K75" s="13" t="n"/>
+      <c r="L75" s="13" t="n"/>
+      <c r="M75" s="13" t="n"/>
       <c r="N75" s="5" t="n"/>
       <c r="O75" s="5" t="n"/>
       <c r="P75" s="5" t="n"/>
@@ -2485,13 +2492,13 @@
       <c r="D76" s="4" t="n"/>
       <c r="E76" s="4" t="n"/>
       <c r="F76" s="4" t="n"/>
-      <c r="G76" s="4" t="n"/>
+      <c r="G76" s="13" t="n"/>
       <c r="H76" s="4" t="n"/>
       <c r="I76" s="4" t="n"/>
-      <c r="J76" s="4" t="n"/>
-      <c r="K76" s="4" t="n"/>
-      <c r="L76" s="4" t="n"/>
-      <c r="M76" s="4" t="n"/>
+      <c r="J76" s="13" t="n"/>
+      <c r="K76" s="13" t="n"/>
+      <c r="L76" s="13" t="n"/>
+      <c r="M76" s="13" t="n"/>
       <c r="N76" s="5" t="n"/>
       <c r="O76" s="5" t="n"/>
       <c r="P76" s="5" t="n"/>
@@ -2507,13 +2514,13 @@
       <c r="D77" s="4" t="n"/>
       <c r="E77" s="4" t="n"/>
       <c r="F77" s="4" t="n"/>
-      <c r="G77" s="4" t="n"/>
+      <c r="G77" s="13" t="n"/>
       <c r="H77" s="4" t="n"/>
       <c r="I77" s="4" t="n"/>
-      <c r="J77" s="4" t="n"/>
-      <c r="K77" s="4" t="n"/>
-      <c r="L77" s="4" t="n"/>
-      <c r="M77" s="4" t="n"/>
+      <c r="J77" s="13" t="n"/>
+      <c r="K77" s="13" t="n"/>
+      <c r="L77" s="13" t="n"/>
+      <c r="M77" s="13" t="n"/>
       <c r="N77" s="5" t="n"/>
       <c r="O77" s="5" t="n"/>
       <c r="P77" s="5" t="n"/>
@@ -2529,13 +2536,13 @@
       <c r="D78" s="4" t="n"/>
       <c r="E78" s="4" t="n"/>
       <c r="F78" s="4" t="n"/>
-      <c r="G78" s="4" t="n"/>
+      <c r="G78" s="13" t="n"/>
       <c r="H78" s="4" t="n"/>
       <c r="I78" s="4" t="n"/>
-      <c r="J78" s="4" t="n"/>
-      <c r="K78" s="4" t="n"/>
-      <c r="L78" s="4" t="n"/>
-      <c r="M78" s="4" t="n"/>
+      <c r="J78" s="13" t="n"/>
+      <c r="K78" s="13" t="n"/>
+      <c r="L78" s="13" t="n"/>
+      <c r="M78" s="13" t="n"/>
       <c r="N78" s="5" t="n"/>
       <c r="O78" s="5" t="n"/>
       <c r="P78" s="5" t="n"/>
@@ -2551,13 +2558,13 @@
       <c r="D79" s="4" t="n"/>
       <c r="E79" s="4" t="n"/>
       <c r="F79" s="4" t="n"/>
-      <c r="G79" s="4" t="n"/>
+      <c r="G79" s="13" t="n"/>
       <c r="H79" s="4" t="n"/>
       <c r="I79" s="4" t="n"/>
-      <c r="J79" s="4" t="n"/>
-      <c r="K79" s="4" t="n"/>
-      <c r="L79" s="4" t="n"/>
-      <c r="M79" s="4" t="n"/>
+      <c r="J79" s="13" t="n"/>
+      <c r="K79" s="13" t="n"/>
+      <c r="L79" s="13" t="n"/>
+      <c r="M79" s="13" t="n"/>
       <c r="N79" s="5" t="n"/>
       <c r="O79" s="5" t="n"/>
       <c r="P79" s="5" t="n"/>
@@ -2573,13 +2580,13 @@
       <c r="D80" s="4" t="n"/>
       <c r="E80" s="4" t="n"/>
       <c r="F80" s="4" t="n"/>
-      <c r="G80" s="4" t="n"/>
+      <c r="G80" s="13" t="n"/>
       <c r="H80" s="4" t="n"/>
       <c r="I80" s="4" t="n"/>
-      <c r="J80" s="4" t="n"/>
-      <c r="K80" s="4" t="n"/>
-      <c r="L80" s="4" t="n"/>
-      <c r="M80" s="4" t="n"/>
+      <c r="J80" s="13" t="n"/>
+      <c r="K80" s="13" t="n"/>
+      <c r="L80" s="13" t="n"/>
+      <c r="M80" s="13" t="n"/>
       <c r="N80" s="5" t="n"/>
       <c r="O80" s="5" t="n"/>
       <c r="P80" s="5" t="n"/>
@@ -2595,13 +2602,13 @@
       <c r="D81" s="4" t="n"/>
       <c r="E81" s="4" t="n"/>
       <c r="F81" s="4" t="n"/>
-      <c r="G81" s="4" t="n"/>
+      <c r="G81" s="13" t="n"/>
       <c r="H81" s="4" t="n"/>
       <c r="I81" s="4" t="n"/>
-      <c r="J81" s="4" t="n"/>
-      <c r="K81" s="4" t="n"/>
-      <c r="L81" s="4" t="n"/>
-      <c r="M81" s="4" t="n"/>
+      <c r="J81" s="13" t="n"/>
+      <c r="K81" s="13" t="n"/>
+      <c r="L81" s="13" t="n"/>
+      <c r="M81" s="13" t="n"/>
       <c r="N81" s="5" t="n"/>
       <c r="O81" s="5" t="n"/>
       <c r="P81" s="5" t="n"/>
@@ -2617,13 +2624,13 @@
       <c r="D82" s="4" t="n"/>
       <c r="E82" s="4" t="n"/>
       <c r="F82" s="4" t="n"/>
-      <c r="G82" s="4" t="n"/>
+      <c r="G82" s="13" t="n"/>
       <c r="H82" s="4" t="n"/>
       <c r="I82" s="4" t="n"/>
-      <c r="J82" s="4" t="n"/>
-      <c r="K82" s="4" t="n"/>
-      <c r="L82" s="4" t="n"/>
-      <c r="M82" s="4" t="n"/>
+      <c r="J82" s="13" t="n"/>
+      <c r="K82" s="13" t="n"/>
+      <c r="L82" s="13" t="n"/>
+      <c r="M82" s="13" t="n"/>
       <c r="N82" s="5" t="n"/>
       <c r="O82" s="5" t="n"/>
       <c r="P82" s="5" t="n"/>
@@ -2639,13 +2646,13 @@
       <c r="D83" s="4" t="n"/>
       <c r="E83" s="4" t="n"/>
       <c r="F83" s="4" t="n"/>
-      <c r="G83" s="4" t="n"/>
+      <c r="G83" s="13" t="n"/>
       <c r="H83" s="4" t="n"/>
       <c r="I83" s="4" t="n"/>
-      <c r="J83" s="4" t="n"/>
-      <c r="K83" s="4" t="n"/>
-      <c r="L83" s="4" t="n"/>
-      <c r="M83" s="4" t="n"/>
+      <c r="J83" s="13" t="n"/>
+      <c r="K83" s="13" t="n"/>
+      <c r="L83" s="13" t="n"/>
+      <c r="M83" s="13" t="n"/>
       <c r="N83" s="5" t="n"/>
       <c r="O83" s="5" t="n"/>
       <c r="P83" s="5" t="n"/>
@@ -2661,13 +2668,13 @@
       <c r="D84" s="4" t="n"/>
       <c r="E84" s="4" t="n"/>
       <c r="F84" s="4" t="n"/>
-      <c r="G84" s="4" t="n"/>
+      <c r="G84" s="13" t="n"/>
       <c r="H84" s="4" t="n"/>
       <c r="I84" s="4" t="n"/>
-      <c r="J84" s="4" t="n"/>
-      <c r="K84" s="4" t="n"/>
-      <c r="L84" s="4" t="n"/>
-      <c r="M84" s="4" t="n"/>
+      <c r="J84" s="13" t="n"/>
+      <c r="K84" s="13" t="n"/>
+      <c r="L84" s="13" t="n"/>
+      <c r="M84" s="13" t="n"/>
       <c r="N84" s="5" t="n"/>
       <c r="O84" s="5" t="n"/>
       <c r="P84" s="5" t="n"/>
@@ -2683,13 +2690,13 @@
       <c r="D85" s="4" t="n"/>
       <c r="E85" s="4" t="n"/>
       <c r="F85" s="4" t="n"/>
-      <c r="G85" s="4" t="n"/>
+      <c r="G85" s="13" t="n"/>
       <c r="H85" s="4" t="n"/>
       <c r="I85" s="4" t="n"/>
-      <c r="J85" s="4" t="n"/>
-      <c r="K85" s="4" t="n"/>
-      <c r="L85" s="4" t="n"/>
-      <c r="M85" s="4" t="n"/>
+      <c r="J85" s="13" t="n"/>
+      <c r="K85" s="13" t="n"/>
+      <c r="L85" s="13" t="n"/>
+      <c r="M85" s="13" t="n"/>
       <c r="N85" s="5" t="n"/>
       <c r="O85" s="5" t="n"/>
       <c r="P85" s="5" t="n"/>
@@ -2705,13 +2712,13 @@
       <c r="D86" s="4" t="n"/>
       <c r="E86" s="4" t="n"/>
       <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
+      <c r="G86" s="13" t="n"/>
       <c r="H86" s="4" t="n"/>
       <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="n"/>
-      <c r="K86" s="4" t="n"/>
-      <c r="L86" s="4" t="n"/>
-      <c r="M86" s="4" t="n"/>
+      <c r="J86" s="13" t="n"/>
+      <c r="K86" s="13" t="n"/>
+      <c r="L86" s="13" t="n"/>
+      <c r="M86" s="13" t="n"/>
       <c r="N86" s="5" t="n"/>
       <c r="O86" s="5" t="n"/>
       <c r="P86" s="5" t="n"/>
@@ -2727,13 +2734,13 @@
       <c r="D87" s="4" t="n"/>
       <c r="E87" s="4" t="n"/>
       <c r="F87" s="4" t="n"/>
-      <c r="G87" s="4" t="n"/>
+      <c r="G87" s="13" t="n"/>
       <c r="H87" s="4" t="n"/>
       <c r="I87" s="4" t="n"/>
-      <c r="J87" s="4" t="n"/>
-      <c r="K87" s="4" t="n"/>
-      <c r="L87" s="4" t="n"/>
-      <c r="M87" s="4" t="n"/>
+      <c r="J87" s="13" t="n"/>
+      <c r="K87" s="13" t="n"/>
+      <c r="L87" s="13" t="n"/>
+      <c r="M87" s="13" t="n"/>
       <c r="N87" s="5" t="n"/>
       <c r="O87" s="5" t="n"/>
       <c r="P87" s="5" t="n"/>
@@ -2749,13 +2756,13 @@
       <c r="D88" s="4" t="n"/>
       <c r="E88" s="4" t="n"/>
       <c r="F88" s="4" t="n"/>
-      <c r="G88" s="4" t="n"/>
+      <c r="G88" s="13" t="n"/>
       <c r="H88" s="4" t="n"/>
       <c r="I88" s="4" t="n"/>
-      <c r="J88" s="4" t="n"/>
-      <c r="K88" s="4" t="n"/>
-      <c r="L88" s="4" t="n"/>
-      <c r="M88" s="4" t="n"/>
+      <c r="J88" s="13" t="n"/>
+      <c r="K88" s="13" t="n"/>
+      <c r="L88" s="13" t="n"/>
+      <c r="M88" s="13" t="n"/>
       <c r="N88" s="5" t="n"/>
       <c r="O88" s="5" t="n"/>
       <c r="P88" s="5" t="n"/>
@@ -2771,13 +2778,13 @@
       <c r="D89" s="4" t="n"/>
       <c r="E89" s="4" t="n"/>
       <c r="F89" s="4" t="n"/>
-      <c r="G89" s="4" t="n"/>
+      <c r="G89" s="13" t="n"/>
       <c r="H89" s="4" t="n"/>
       <c r="I89" s="4" t="n"/>
-      <c r="J89" s="4" t="n"/>
-      <c r="K89" s="4" t="n"/>
-      <c r="L89" s="4" t="n"/>
-      <c r="M89" s="4" t="n"/>
+      <c r="J89" s="13" t="n"/>
+      <c r="K89" s="13" t="n"/>
+      <c r="L89" s="13" t="n"/>
+      <c r="M89" s="13" t="n"/>
       <c r="N89" s="5" t="n"/>
       <c r="O89" s="5" t="n"/>
       <c r="P89" s="5" t="n"/>
@@ -2793,13 +2800,13 @@
       <c r="D90" s="4" t="n"/>
       <c r="E90" s="4" t="n"/>
       <c r="F90" s="4" t="n"/>
-      <c r="G90" s="4" t="n"/>
+      <c r="G90" s="13" t="n"/>
       <c r="H90" s="4" t="n"/>
       <c r="I90" s="4" t="n"/>
-      <c r="J90" s="4" t="n"/>
-      <c r="K90" s="4" t="n"/>
-      <c r="L90" s="4" t="n"/>
-      <c r="M90" s="4" t="n"/>
+      <c r="J90" s="13" t="n"/>
+      <c r="K90" s="13" t="n"/>
+      <c r="L90" s="13" t="n"/>
+      <c r="M90" s="13" t="n"/>
       <c r="N90" s="5" t="n"/>
       <c r="O90" s="5" t="n"/>
       <c r="P90" s="5" t="n"/>
@@ -2815,13 +2822,13 @@
       <c r="D91" s="4" t="n"/>
       <c r="E91" s="4" t="n"/>
       <c r="F91" s="4" t="n"/>
-      <c r="G91" s="4" t="n"/>
+      <c r="G91" s="13" t="n"/>
       <c r="H91" s="4" t="n"/>
       <c r="I91" s="4" t="n"/>
-      <c r="J91" s="4" t="n"/>
-      <c r="K91" s="4" t="n"/>
-      <c r="L91" s="4" t="n"/>
-      <c r="M91" s="4" t="n"/>
+      <c r="J91" s="13" t="n"/>
+      <c r="K91" s="13" t="n"/>
+      <c r="L91" s="13" t="n"/>
+      <c r="M91" s="13" t="n"/>
       <c r="N91" s="5" t="n"/>
       <c r="O91" s="5" t="n"/>
       <c r="P91" s="5" t="n"/>
@@ -2837,13 +2844,13 @@
       <c r="D92" s="4" t="n"/>
       <c r="E92" s="4" t="n"/>
       <c r="F92" s="4" t="n"/>
-      <c r="G92" s="4" t="n"/>
+      <c r="G92" s="13" t="n"/>
       <c r="H92" s="4" t="n"/>
       <c r="I92" s="4" t="n"/>
-      <c r="J92" s="4" t="n"/>
-      <c r="K92" s="4" t="n"/>
-      <c r="L92" s="4" t="n"/>
-      <c r="M92" s="4" t="n"/>
+      <c r="J92" s="13" t="n"/>
+      <c r="K92" s="13" t="n"/>
+      <c r="L92" s="13" t="n"/>
+      <c r="M92" s="13" t="n"/>
       <c r="N92" s="5" t="n"/>
       <c r="O92" s="5" t="n"/>
       <c r="P92" s="5" t="n"/>
@@ -2859,13 +2866,13 @@
       <c r="D93" s="4" t="n"/>
       <c r="E93" s="4" t="n"/>
       <c r="F93" s="4" t="n"/>
-      <c r="G93" s="4" t="n"/>
+      <c r="G93" s="13" t="n"/>
       <c r="H93" s="4" t="n"/>
       <c r="I93" s="4" t="n"/>
-      <c r="J93" s="4" t="n"/>
-      <c r="K93" s="4" t="n"/>
-      <c r="L93" s="4" t="n"/>
-      <c r="M93" s="4" t="n"/>
+      <c r="J93" s="13" t="n"/>
+      <c r="K93" s="13" t="n"/>
+      <c r="L93" s="13" t="n"/>
+      <c r="M93" s="13" t="n"/>
       <c r="N93" s="5" t="n"/>
       <c r="O93" s="5" t="n"/>
       <c r="P93" s="5" t="n"/>
@@ -2881,13 +2888,13 @@
       <c r="D94" s="4" t="n"/>
       <c r="E94" s="4" t="n"/>
       <c r="F94" s="4" t="n"/>
-      <c r="G94" s="4" t="n"/>
+      <c r="G94" s="13" t="n"/>
       <c r="H94" s="4" t="n"/>
       <c r="I94" s="4" t="n"/>
-      <c r="J94" s="4" t="n"/>
-      <c r="K94" s="4" t="n"/>
-      <c r="L94" s="4" t="n"/>
-      <c r="M94" s="4" t="n"/>
+      <c r="J94" s="13" t="n"/>
+      <c r="K94" s="13" t="n"/>
+      <c r="L94" s="13" t="n"/>
+      <c r="M94" s="13" t="n"/>
       <c r="N94" s="5" t="n"/>
       <c r="O94" s="5" t="n"/>
       <c r="P94" s="5" t="n"/>
@@ -2903,13 +2910,13 @@
       <c r="D95" s="4" t="n"/>
       <c r="E95" s="4" t="n"/>
       <c r="F95" s="4" t="n"/>
-      <c r="G95" s="4" t="n"/>
+      <c r="G95" s="13" t="n"/>
       <c r="H95" s="4" t="n"/>
       <c r="I95" s="4" t="n"/>
-      <c r="J95" s="4" t="n"/>
-      <c r="K95" s="4" t="n"/>
-      <c r="L95" s="4" t="n"/>
-      <c r="M95" s="4" t="n"/>
+      <c r="J95" s="13" t="n"/>
+      <c r="K95" s="13" t="n"/>
+      <c r="L95" s="13" t="n"/>
+      <c r="M95" s="13" t="n"/>
       <c r="N95" s="5" t="n"/>
       <c r="O95" s="5" t="n"/>
       <c r="P95" s="5" t="n"/>
@@ -2925,13 +2932,13 @@
       <c r="D96" s="4" t="n"/>
       <c r="E96" s="4" t="n"/>
       <c r="F96" s="4" t="n"/>
-      <c r="G96" s="4" t="n"/>
+      <c r="G96" s="13" t="n"/>
       <c r="H96" s="4" t="n"/>
       <c r="I96" s="4" t="n"/>
-      <c r="J96" s="4" t="n"/>
-      <c r="K96" s="4" t="n"/>
-      <c r="L96" s="4" t="n"/>
-      <c r="M96" s="4" t="n"/>
+      <c r="J96" s="13" t="n"/>
+      <c r="K96" s="13" t="n"/>
+      <c r="L96" s="13" t="n"/>
+      <c r="M96" s="13" t="n"/>
       <c r="N96" s="5" t="n"/>
       <c r="O96" s="5" t="n"/>
       <c r="P96" s="5" t="n"/>
@@ -2947,13 +2954,13 @@
       <c r="D97" s="4" t="n"/>
       <c r="E97" s="4" t="n"/>
       <c r="F97" s="4" t="n"/>
-      <c r="G97" s="4" t="n"/>
+      <c r="G97" s="13" t="n"/>
       <c r="H97" s="4" t="n"/>
       <c r="I97" s="4" t="n"/>
-      <c r="J97" s="4" t="n"/>
-      <c r="K97" s="4" t="n"/>
-      <c r="L97" s="4" t="n"/>
-      <c r="M97" s="4" t="n"/>
+      <c r="J97" s="13" t="n"/>
+      <c r="K97" s="13" t="n"/>
+      <c r="L97" s="13" t="n"/>
+      <c r="M97" s="13" t="n"/>
       <c r="N97" s="5" t="n"/>
       <c r="O97" s="5" t="n"/>
       <c r="P97" s="5" t="n"/>
@@ -2969,13 +2976,13 @@
       <c r="D98" s="4" t="n"/>
       <c r="E98" s="4" t="n"/>
       <c r="F98" s="4" t="n"/>
-      <c r="G98" s="4" t="n"/>
+      <c r="G98" s="13" t="n"/>
       <c r="H98" s="4" t="n"/>
       <c r="I98" s="4" t="n"/>
-      <c r="J98" s="4" t="n"/>
-      <c r="K98" s="4" t="n"/>
-      <c r="L98" s="4" t="n"/>
-      <c r="M98" s="4" t="n"/>
+      <c r="J98" s="13" t="n"/>
+      <c r="K98" s="13" t="n"/>
+      <c r="L98" s="13" t="n"/>
+      <c r="M98" s="13" t="n"/>
       <c r="N98" s="5" t="n"/>
       <c r="O98" s="5" t="n"/>
       <c r="P98" s="5" t="n"/>
@@ -2991,13 +2998,13 @@
       <c r="D99" s="4" t="n"/>
       <c r="E99" s="4" t="n"/>
       <c r="F99" s="4" t="n"/>
-      <c r="G99" s="4" t="n"/>
+      <c r="G99" s="13" t="n"/>
       <c r="H99" s="4" t="n"/>
       <c r="I99" s="4" t="n"/>
-      <c r="J99" s="4" t="n"/>
-      <c r="K99" s="4" t="n"/>
-      <c r="L99" s="4" t="n"/>
-      <c r="M99" s="4" t="n"/>
+      <c r="J99" s="13" t="n"/>
+      <c r="K99" s="13" t="n"/>
+      <c r="L99" s="13" t="n"/>
+      <c r="M99" s="13" t="n"/>
       <c r="N99" s="5" t="n"/>
       <c r="O99" s="5" t="n"/>
       <c r="P99" s="5" t="n"/>
@@ -3013,13 +3020,13 @@
       <c r="D100" s="4" t="n"/>
       <c r="E100" s="4" t="n"/>
       <c r="F100" s="4" t="n"/>
-      <c r="G100" s="4" t="n"/>
+      <c r="G100" s="13" t="n"/>
       <c r="H100" s="4" t="n"/>
       <c r="I100" s="4" t="n"/>
-      <c r="J100" s="4" t="n"/>
-      <c r="K100" s="4" t="n"/>
-      <c r="L100" s="4" t="n"/>
-      <c r="M100" s="4" t="n"/>
+      <c r="J100" s="13" t="n"/>
+      <c r="K100" s="13" t="n"/>
+      <c r="L100" s="13" t="n"/>
+      <c r="M100" s="13" t="n"/>
       <c r="N100" s="5" t="n"/>
       <c r="O100" s="5" t="n"/>
       <c r="P100" s="5" t="n"/>
@@ -3035,13 +3042,13 @@
       <c r="D101" s="4" t="n"/>
       <c r="E101" s="4" t="n"/>
       <c r="F101" s="4" t="n"/>
-      <c r="G101" s="4" t="n"/>
+      <c r="G101" s="13" t="n"/>
       <c r="H101" s="4" t="n"/>
       <c r="I101" s="4" t="n"/>
-      <c r="J101" s="4" t="n"/>
-      <c r="K101" s="4" t="n"/>
-      <c r="L101" s="4" t="n"/>
-      <c r="M101" s="4" t="n"/>
+      <c r="J101" s="13" t="n"/>
+      <c r="K101" s="13" t="n"/>
+      <c r="L101" s="13" t="n"/>
+      <c r="M101" s="13" t="n"/>
       <c r="N101" s="5" t="n"/>
       <c r="O101" s="5" t="n"/>
       <c r="P101" s="5" t="n"/>
@@ -3057,13 +3064,13 @@
       <c r="D102" s="4" t="n"/>
       <c r="E102" s="4" t="n"/>
       <c r="F102" s="4" t="n"/>
-      <c r="G102" s="4" t="n"/>
+      <c r="G102" s="13" t="n"/>
       <c r="H102" s="4" t="n"/>
       <c r="I102" s="4" t="n"/>
-      <c r="J102" s="4" t="n"/>
-      <c r="K102" s="4" t="n"/>
-      <c r="L102" s="4" t="n"/>
-      <c r="M102" s="4" t="n"/>
+      <c r="J102" s="13" t="n"/>
+      <c r="K102" s="13" t="n"/>
+      <c r="L102" s="13" t="n"/>
+      <c r="M102" s="13" t="n"/>
       <c r="N102" s="5" t="n"/>
       <c r="O102" s="5" t="n"/>
       <c r="P102" s="5" t="n"/>
@@ -3079,13 +3086,13 @@
       <c r="D103" s="4" t="n"/>
       <c r="E103" s="4" t="n"/>
       <c r="F103" s="4" t="n"/>
-      <c r="G103" s="4" t="n"/>
+      <c r="G103" s="13" t="n"/>
       <c r="H103" s="4" t="n"/>
       <c r="I103" s="4" t="n"/>
-      <c r="J103" s="4" t="n"/>
-      <c r="K103" s="4" t="n"/>
-      <c r="L103" s="4" t="n"/>
-      <c r="M103" s="4" t="n"/>
+      <c r="J103" s="13" t="n"/>
+      <c r="K103" s="13" t="n"/>
+      <c r="L103" s="13" t="n"/>
+      <c r="M103" s="13" t="n"/>
       <c r="N103" s="5" t="n"/>
       <c r="O103" s="5" t="n"/>
       <c r="P103" s="5" t="n"/>
@@ -3093,6 +3100,1385 @@
       <c r="R103" s="4" t="n"/>
       <c r="S103" s="4" t="n"/>
       <c r="T103" s="4" t="n"/>
+    </row>
+    <row r="104">
+      <c r="G104" s="14" t="n"/>
+      <c r="J104" s="14" t="n"/>
+      <c r="K104" s="14" t="n"/>
+      <c r="L104" s="14" t="n"/>
+      <c r="M104" s="14" t="n"/>
+    </row>
+    <row r="105">
+      <c r="G105" s="14" t="n"/>
+      <c r="J105" s="14" t="n"/>
+      <c r="K105" s="14" t="n"/>
+      <c r="L105" s="14" t="n"/>
+      <c r="M105" s="14" t="n"/>
+    </row>
+    <row r="106">
+      <c r="G106" s="14" t="n"/>
+      <c r="J106" s="14" t="n"/>
+      <c r="K106" s="14" t="n"/>
+      <c r="L106" s="14" t="n"/>
+      <c r="M106" s="14" t="n"/>
+    </row>
+    <row r="107">
+      <c r="G107" s="14" t="n"/>
+      <c r="J107" s="14" t="n"/>
+      <c r="K107" s="14" t="n"/>
+      <c r="L107" s="14" t="n"/>
+      <c r="M107" s="14" t="n"/>
+    </row>
+    <row r="108">
+      <c r="G108" s="14" t="n"/>
+      <c r="J108" s="14" t="n"/>
+      <c r="K108" s="14" t="n"/>
+      <c r="L108" s="14" t="n"/>
+      <c r="M108" s="14" t="n"/>
+    </row>
+    <row r="109">
+      <c r="G109" s="14" t="n"/>
+      <c r="J109" s="14" t="n"/>
+      <c r="K109" s="14" t="n"/>
+      <c r="L109" s="14" t="n"/>
+      <c r="M109" s="14" t="n"/>
+    </row>
+    <row r="110">
+      <c r="G110" s="14" t="n"/>
+      <c r="J110" s="14" t="n"/>
+      <c r="K110" s="14" t="n"/>
+      <c r="L110" s="14" t="n"/>
+      <c r="M110" s="14" t="n"/>
+    </row>
+    <row r="111">
+      <c r="G111" s="14" t="n"/>
+      <c r="J111" s="14" t="n"/>
+      <c r="K111" s="14" t="n"/>
+      <c r="L111" s="14" t="n"/>
+      <c r="M111" s="14" t="n"/>
+    </row>
+    <row r="112">
+      <c r="G112" s="14" t="n"/>
+      <c r="J112" s="14" t="n"/>
+      <c r="K112" s="14" t="n"/>
+      <c r="L112" s="14" t="n"/>
+      <c r="M112" s="14" t="n"/>
+    </row>
+    <row r="113">
+      <c r="G113" s="14" t="n"/>
+      <c r="J113" s="14" t="n"/>
+      <c r="K113" s="14" t="n"/>
+      <c r="L113" s="14" t="n"/>
+      <c r="M113" s="14" t="n"/>
+    </row>
+    <row r="114">
+      <c r="G114" s="14" t="n"/>
+      <c r="J114" s="14" t="n"/>
+      <c r="K114" s="14" t="n"/>
+      <c r="L114" s="14" t="n"/>
+      <c r="M114" s="14" t="n"/>
+    </row>
+    <row r="115">
+      <c r="G115" s="14" t="n"/>
+      <c r="J115" s="14" t="n"/>
+      <c r="K115" s="14" t="n"/>
+      <c r="L115" s="14" t="n"/>
+      <c r="M115" s="14" t="n"/>
+    </row>
+    <row r="116">
+      <c r="G116" s="14" t="n"/>
+      <c r="J116" s="14" t="n"/>
+      <c r="K116" s="14" t="n"/>
+      <c r="L116" s="14" t="n"/>
+      <c r="M116" s="14" t="n"/>
+    </row>
+    <row r="117">
+      <c r="G117" s="14" t="n"/>
+      <c r="J117" s="14" t="n"/>
+      <c r="K117" s="14" t="n"/>
+      <c r="L117" s="14" t="n"/>
+      <c r="M117" s="14" t="n"/>
+    </row>
+    <row r="118">
+      <c r="G118" s="14" t="n"/>
+      <c r="J118" s="14" t="n"/>
+      <c r="K118" s="14" t="n"/>
+      <c r="L118" s="14" t="n"/>
+      <c r="M118" s="14" t="n"/>
+    </row>
+    <row r="119">
+      <c r="G119" s="14" t="n"/>
+      <c r="J119" s="14" t="n"/>
+      <c r="K119" s="14" t="n"/>
+      <c r="L119" s="14" t="n"/>
+      <c r="M119" s="14" t="n"/>
+    </row>
+    <row r="120">
+      <c r="G120" s="14" t="n"/>
+      <c r="J120" s="14" t="n"/>
+      <c r="K120" s="14" t="n"/>
+      <c r="L120" s="14" t="n"/>
+      <c r="M120" s="14" t="n"/>
+    </row>
+    <row r="121">
+      <c r="G121" s="14" t="n"/>
+      <c r="J121" s="14" t="n"/>
+      <c r="K121" s="14" t="n"/>
+      <c r="L121" s="14" t="n"/>
+      <c r="M121" s="14" t="n"/>
+    </row>
+    <row r="122">
+      <c r="G122" s="14" t="n"/>
+      <c r="J122" s="14" t="n"/>
+      <c r="K122" s="14" t="n"/>
+      <c r="L122" s="14" t="n"/>
+      <c r="M122" s="14" t="n"/>
+    </row>
+    <row r="123">
+      <c r="G123" s="14" t="n"/>
+      <c r="J123" s="14" t="n"/>
+      <c r="K123" s="14" t="n"/>
+      <c r="L123" s="14" t="n"/>
+      <c r="M123" s="14" t="n"/>
+    </row>
+    <row r="124">
+      <c r="G124" s="14" t="n"/>
+      <c r="J124" s="14" t="n"/>
+      <c r="K124" s="14" t="n"/>
+      <c r="L124" s="14" t="n"/>
+      <c r="M124" s="14" t="n"/>
+    </row>
+    <row r="125">
+      <c r="G125" s="14" t="n"/>
+      <c r="J125" s="14" t="n"/>
+      <c r="K125" s="14" t="n"/>
+      <c r="L125" s="14" t="n"/>
+      <c r="M125" s="14" t="n"/>
+    </row>
+    <row r="126">
+      <c r="G126" s="14" t="n"/>
+      <c r="J126" s="14" t="n"/>
+      <c r="K126" s="14" t="n"/>
+      <c r="L126" s="14" t="n"/>
+      <c r="M126" s="14" t="n"/>
+    </row>
+    <row r="127">
+      <c r="G127" s="14" t="n"/>
+      <c r="J127" s="14" t="n"/>
+      <c r="K127" s="14" t="n"/>
+      <c r="L127" s="14" t="n"/>
+      <c r="M127" s="14" t="n"/>
+    </row>
+    <row r="128">
+      <c r="G128" s="14" t="n"/>
+      <c r="J128" s="14" t="n"/>
+      <c r="K128" s="14" t="n"/>
+      <c r="L128" s="14" t="n"/>
+      <c r="M128" s="14" t="n"/>
+    </row>
+    <row r="129">
+      <c r="G129" s="14" t="n"/>
+      <c r="J129" s="14" t="n"/>
+      <c r="K129" s="14" t="n"/>
+      <c r="L129" s="14" t="n"/>
+      <c r="M129" s="14" t="n"/>
+    </row>
+    <row r="130">
+      <c r="G130" s="14" t="n"/>
+      <c r="J130" s="14" t="n"/>
+      <c r="K130" s="14" t="n"/>
+      <c r="L130" s="14" t="n"/>
+      <c r="M130" s="14" t="n"/>
+    </row>
+    <row r="131">
+      <c r="G131" s="14" t="n"/>
+      <c r="J131" s="14" t="n"/>
+      <c r="K131" s="14" t="n"/>
+      <c r="L131" s="14" t="n"/>
+      <c r="M131" s="14" t="n"/>
+    </row>
+    <row r="132">
+      <c r="G132" s="14" t="n"/>
+      <c r="J132" s="14" t="n"/>
+      <c r="K132" s="14" t="n"/>
+      <c r="L132" s="14" t="n"/>
+      <c r="M132" s="14" t="n"/>
+    </row>
+    <row r="133">
+      <c r="G133" s="14" t="n"/>
+      <c r="J133" s="14" t="n"/>
+      <c r="K133" s="14" t="n"/>
+      <c r="L133" s="14" t="n"/>
+      <c r="M133" s="14" t="n"/>
+    </row>
+    <row r="134">
+      <c r="G134" s="14" t="n"/>
+      <c r="J134" s="14" t="n"/>
+      <c r="K134" s="14" t="n"/>
+      <c r="L134" s="14" t="n"/>
+      <c r="M134" s="14" t="n"/>
+    </row>
+    <row r="135">
+      <c r="G135" s="14" t="n"/>
+      <c r="J135" s="14" t="n"/>
+      <c r="K135" s="14" t="n"/>
+      <c r="L135" s="14" t="n"/>
+      <c r="M135" s="14" t="n"/>
+    </row>
+    <row r="136">
+      <c r="G136" s="14" t="n"/>
+      <c r="J136" s="14" t="n"/>
+      <c r="K136" s="14" t="n"/>
+      <c r="L136" s="14" t="n"/>
+      <c r="M136" s="14" t="n"/>
+    </row>
+    <row r="137">
+      <c r="G137" s="14" t="n"/>
+      <c r="J137" s="14" t="n"/>
+      <c r="K137" s="14" t="n"/>
+      <c r="L137" s="14" t="n"/>
+      <c r="M137" s="14" t="n"/>
+    </row>
+    <row r="138">
+      <c r="G138" s="14" t="n"/>
+      <c r="J138" s="14" t="n"/>
+      <c r="K138" s="14" t="n"/>
+      <c r="L138" s="14" t="n"/>
+      <c r="M138" s="14" t="n"/>
+    </row>
+    <row r="139">
+      <c r="G139" s="14" t="n"/>
+      <c r="J139" s="14" t="n"/>
+      <c r="K139" s="14" t="n"/>
+      <c r="L139" s="14" t="n"/>
+      <c r="M139" s="14" t="n"/>
+    </row>
+    <row r="140">
+      <c r="G140" s="14" t="n"/>
+      <c r="J140" s="14" t="n"/>
+      <c r="K140" s="14" t="n"/>
+      <c r="L140" s="14" t="n"/>
+      <c r="M140" s="14" t="n"/>
+    </row>
+    <row r="141">
+      <c r="G141" s="14" t="n"/>
+      <c r="J141" s="14" t="n"/>
+      <c r="K141" s="14" t="n"/>
+      <c r="L141" s="14" t="n"/>
+      <c r="M141" s="14" t="n"/>
+    </row>
+    <row r="142">
+      <c r="G142" s="14" t="n"/>
+      <c r="J142" s="14" t="n"/>
+      <c r="K142" s="14" t="n"/>
+      <c r="L142" s="14" t="n"/>
+      <c r="M142" s="14" t="n"/>
+    </row>
+    <row r="143">
+      <c r="G143" s="14" t="n"/>
+      <c r="J143" s="14" t="n"/>
+      <c r="K143" s="14" t="n"/>
+      <c r="L143" s="14" t="n"/>
+      <c r="M143" s="14" t="n"/>
+    </row>
+    <row r="144">
+      <c r="G144" s="14" t="n"/>
+      <c r="J144" s="14" t="n"/>
+      <c r="K144" s="14" t="n"/>
+      <c r="L144" s="14" t="n"/>
+      <c r="M144" s="14" t="n"/>
+    </row>
+    <row r="145">
+      <c r="G145" s="14" t="n"/>
+      <c r="J145" s="14" t="n"/>
+      <c r="K145" s="14" t="n"/>
+      <c r="L145" s="14" t="n"/>
+      <c r="M145" s="14" t="n"/>
+    </row>
+    <row r="146">
+      <c r="G146" s="14" t="n"/>
+      <c r="J146" s="14" t="n"/>
+      <c r="K146" s="14" t="n"/>
+      <c r="L146" s="14" t="n"/>
+      <c r="M146" s="14" t="n"/>
+    </row>
+    <row r="147">
+      <c r="G147" s="14" t="n"/>
+      <c r="J147" s="14" t="n"/>
+      <c r="K147" s="14" t="n"/>
+      <c r="L147" s="14" t="n"/>
+      <c r="M147" s="14" t="n"/>
+    </row>
+    <row r="148">
+      <c r="G148" s="14" t="n"/>
+      <c r="J148" s="14" t="n"/>
+      <c r="K148" s="14" t="n"/>
+      <c r="L148" s="14" t="n"/>
+      <c r="M148" s="14" t="n"/>
+    </row>
+    <row r="149">
+      <c r="G149" s="14" t="n"/>
+      <c r="J149" s="14" t="n"/>
+      <c r="K149" s="14" t="n"/>
+      <c r="L149" s="14" t="n"/>
+      <c r="M149" s="14" t="n"/>
+    </row>
+    <row r="150">
+      <c r="G150" s="14" t="n"/>
+      <c r="J150" s="14" t="n"/>
+      <c r="K150" s="14" t="n"/>
+      <c r="L150" s="14" t="n"/>
+      <c r="M150" s="14" t="n"/>
+    </row>
+    <row r="151">
+      <c r="G151" s="14" t="n"/>
+      <c r="J151" s="14" t="n"/>
+      <c r="K151" s="14" t="n"/>
+      <c r="L151" s="14" t="n"/>
+      <c r="M151" s="14" t="n"/>
+    </row>
+    <row r="152">
+      <c r="G152" s="14" t="n"/>
+      <c r="J152" s="14" t="n"/>
+      <c r="K152" s="14" t="n"/>
+      <c r="L152" s="14" t="n"/>
+      <c r="M152" s="14" t="n"/>
+    </row>
+    <row r="153">
+      <c r="G153" s="14" t="n"/>
+      <c r="J153" s="14" t="n"/>
+      <c r="K153" s="14" t="n"/>
+      <c r="L153" s="14" t="n"/>
+      <c r="M153" s="14" t="n"/>
+    </row>
+    <row r="154">
+      <c r="G154" s="14" t="n"/>
+      <c r="J154" s="14" t="n"/>
+      <c r="K154" s="14" t="n"/>
+      <c r="L154" s="14" t="n"/>
+      <c r="M154" s="14" t="n"/>
+    </row>
+    <row r="155">
+      <c r="G155" s="14" t="n"/>
+      <c r="J155" s="14" t="n"/>
+      <c r="K155" s="14" t="n"/>
+      <c r="L155" s="14" t="n"/>
+      <c r="M155" s="14" t="n"/>
+    </row>
+    <row r="156">
+      <c r="G156" s="14" t="n"/>
+      <c r="J156" s="14" t="n"/>
+      <c r="K156" s="14" t="n"/>
+      <c r="L156" s="14" t="n"/>
+      <c r="M156" s="14" t="n"/>
+    </row>
+    <row r="157">
+      <c r="G157" s="14" t="n"/>
+      <c r="J157" s="14" t="n"/>
+      <c r="K157" s="14" t="n"/>
+      <c r="L157" s="14" t="n"/>
+      <c r="M157" s="14" t="n"/>
+    </row>
+    <row r="158">
+      <c r="G158" s="14" t="n"/>
+      <c r="J158" s="14" t="n"/>
+      <c r="K158" s="14" t="n"/>
+      <c r="L158" s="14" t="n"/>
+      <c r="M158" s="14" t="n"/>
+    </row>
+    <row r="159">
+      <c r="G159" s="14" t="n"/>
+      <c r="J159" s="14" t="n"/>
+      <c r="K159" s="14" t="n"/>
+      <c r="L159" s="14" t="n"/>
+      <c r="M159" s="14" t="n"/>
+    </row>
+    <row r="160">
+      <c r="G160" s="14" t="n"/>
+      <c r="J160" s="14" t="n"/>
+      <c r="K160" s="14" t="n"/>
+      <c r="L160" s="14" t="n"/>
+      <c r="M160" s="14" t="n"/>
+    </row>
+    <row r="161">
+      <c r="G161" s="14" t="n"/>
+      <c r="J161" s="14" t="n"/>
+      <c r="K161" s="14" t="n"/>
+      <c r="L161" s="14" t="n"/>
+      <c r="M161" s="14" t="n"/>
+    </row>
+    <row r="162">
+      <c r="G162" s="14" t="n"/>
+      <c r="J162" s="14" t="n"/>
+      <c r="K162" s="14" t="n"/>
+      <c r="L162" s="14" t="n"/>
+      <c r="M162" s="14" t="n"/>
+    </row>
+    <row r="163">
+      <c r="G163" s="14" t="n"/>
+      <c r="J163" s="14" t="n"/>
+      <c r="K163" s="14" t="n"/>
+      <c r="L163" s="14" t="n"/>
+      <c r="M163" s="14" t="n"/>
+    </row>
+    <row r="164">
+      <c r="G164" s="14" t="n"/>
+      <c r="J164" s="14" t="n"/>
+      <c r="K164" s="14" t="n"/>
+      <c r="L164" s="14" t="n"/>
+      <c r="M164" s="14" t="n"/>
+    </row>
+    <row r="165">
+      <c r="G165" s="14" t="n"/>
+      <c r="J165" s="14" t="n"/>
+      <c r="K165" s="14" t="n"/>
+      <c r="L165" s="14" t="n"/>
+      <c r="M165" s="14" t="n"/>
+    </row>
+    <row r="166">
+      <c r="G166" s="14" t="n"/>
+      <c r="J166" s="14" t="n"/>
+      <c r="K166" s="14" t="n"/>
+      <c r="L166" s="14" t="n"/>
+      <c r="M166" s="14" t="n"/>
+    </row>
+    <row r="167">
+      <c r="G167" s="14" t="n"/>
+      <c r="J167" s="14" t="n"/>
+      <c r="K167" s="14" t="n"/>
+      <c r="L167" s="14" t="n"/>
+      <c r="M167" s="14" t="n"/>
+    </row>
+    <row r="168">
+      <c r="G168" s="14" t="n"/>
+      <c r="J168" s="14" t="n"/>
+      <c r="K168" s="14" t="n"/>
+      <c r="L168" s="14" t="n"/>
+      <c r="M168" s="14" t="n"/>
+    </row>
+    <row r="169">
+      <c r="G169" s="14" t="n"/>
+      <c r="J169" s="14" t="n"/>
+      <c r="K169" s="14" t="n"/>
+      <c r="L169" s="14" t="n"/>
+      <c r="M169" s="14" t="n"/>
+    </row>
+    <row r="170">
+      <c r="G170" s="14" t="n"/>
+      <c r="J170" s="14" t="n"/>
+      <c r="K170" s="14" t="n"/>
+      <c r="L170" s="14" t="n"/>
+      <c r="M170" s="14" t="n"/>
+    </row>
+    <row r="171">
+      <c r="G171" s="14" t="n"/>
+      <c r="J171" s="14" t="n"/>
+      <c r="K171" s="14" t="n"/>
+      <c r="L171" s="14" t="n"/>
+      <c r="M171" s="14" t="n"/>
+    </row>
+    <row r="172">
+      <c r="G172" s="14" t="n"/>
+      <c r="J172" s="14" t="n"/>
+      <c r="K172" s="14" t="n"/>
+      <c r="L172" s="14" t="n"/>
+      <c r="M172" s="14" t="n"/>
+    </row>
+    <row r="173">
+      <c r="G173" s="14" t="n"/>
+      <c r="J173" s="14" t="n"/>
+      <c r="K173" s="14" t="n"/>
+      <c r="L173" s="14" t="n"/>
+      <c r="M173" s="14" t="n"/>
+    </row>
+    <row r="174">
+      <c r="G174" s="14" t="n"/>
+      <c r="J174" s="14" t="n"/>
+      <c r="K174" s="14" t="n"/>
+      <c r="L174" s="14" t="n"/>
+      <c r="M174" s="14" t="n"/>
+    </row>
+    <row r="175">
+      <c r="G175" s="14" t="n"/>
+      <c r="J175" s="14" t="n"/>
+      <c r="K175" s="14" t="n"/>
+      <c r="L175" s="14" t="n"/>
+      <c r="M175" s="14" t="n"/>
+    </row>
+    <row r="176">
+      <c r="G176" s="14" t="n"/>
+      <c r="J176" s="14" t="n"/>
+      <c r="K176" s="14" t="n"/>
+      <c r="L176" s="14" t="n"/>
+      <c r="M176" s="14" t="n"/>
+    </row>
+    <row r="177">
+      <c r="G177" s="14" t="n"/>
+      <c r="J177" s="14" t="n"/>
+      <c r="K177" s="14" t="n"/>
+      <c r="L177" s="14" t="n"/>
+      <c r="M177" s="14" t="n"/>
+    </row>
+    <row r="178">
+      <c r="G178" s="14" t="n"/>
+      <c r="J178" s="14" t="n"/>
+      <c r="K178" s="14" t="n"/>
+      <c r="L178" s="14" t="n"/>
+      <c r="M178" s="14" t="n"/>
+    </row>
+    <row r="179">
+      <c r="G179" s="14" t="n"/>
+      <c r="J179" s="14" t="n"/>
+      <c r="K179" s="14" t="n"/>
+      <c r="L179" s="14" t="n"/>
+      <c r="M179" s="14" t="n"/>
+    </row>
+    <row r="180">
+      <c r="G180" s="14" t="n"/>
+      <c r="J180" s="14" t="n"/>
+      <c r="K180" s="14" t="n"/>
+      <c r="L180" s="14" t="n"/>
+      <c r="M180" s="14" t="n"/>
+    </row>
+    <row r="181">
+      <c r="G181" s="14" t="n"/>
+      <c r="J181" s="14" t="n"/>
+      <c r="K181" s="14" t="n"/>
+      <c r="L181" s="14" t="n"/>
+      <c r="M181" s="14" t="n"/>
+    </row>
+    <row r="182">
+      <c r="G182" s="14" t="n"/>
+      <c r="J182" s="14" t="n"/>
+      <c r="K182" s="14" t="n"/>
+      <c r="L182" s="14" t="n"/>
+      <c r="M182" s="14" t="n"/>
+    </row>
+    <row r="183">
+      <c r="G183" s="14" t="n"/>
+      <c r="J183" s="14" t="n"/>
+      <c r="K183" s="14" t="n"/>
+      <c r="L183" s="14" t="n"/>
+      <c r="M183" s="14" t="n"/>
+    </row>
+    <row r="184">
+      <c r="G184" s="14" t="n"/>
+      <c r="J184" s="14" t="n"/>
+      <c r="K184" s="14" t="n"/>
+      <c r="L184" s="14" t="n"/>
+      <c r="M184" s="14" t="n"/>
+    </row>
+    <row r="185">
+      <c r="G185" s="14" t="n"/>
+      <c r="J185" s="14" t="n"/>
+      <c r="K185" s="14" t="n"/>
+      <c r="L185" s="14" t="n"/>
+      <c r="M185" s="14" t="n"/>
+    </row>
+    <row r="186">
+      <c r="G186" s="14" t="n"/>
+      <c r="J186" s="14" t="n"/>
+      <c r="K186" s="14" t="n"/>
+      <c r="L186" s="14" t="n"/>
+      <c r="M186" s="14" t="n"/>
+    </row>
+    <row r="187">
+      <c r="G187" s="14" t="n"/>
+      <c r="J187" s="14" t="n"/>
+      <c r="K187" s="14" t="n"/>
+      <c r="L187" s="14" t="n"/>
+      <c r="M187" s="14" t="n"/>
+    </row>
+    <row r="188">
+      <c r="G188" s="14" t="n"/>
+      <c r="J188" s="14" t="n"/>
+      <c r="K188" s="14" t="n"/>
+      <c r="L188" s="14" t="n"/>
+      <c r="M188" s="14" t="n"/>
+    </row>
+    <row r="189">
+      <c r="G189" s="14" t="n"/>
+      <c r="J189" s="14" t="n"/>
+      <c r="K189" s="14" t="n"/>
+      <c r="L189" s="14" t="n"/>
+      <c r="M189" s="14" t="n"/>
+    </row>
+    <row r="190">
+      <c r="G190" s="14" t="n"/>
+      <c r="J190" s="14" t="n"/>
+      <c r="K190" s="14" t="n"/>
+      <c r="L190" s="14" t="n"/>
+      <c r="M190" s="14" t="n"/>
+    </row>
+    <row r="191">
+      <c r="G191" s="14" t="n"/>
+      <c r="J191" s="14" t="n"/>
+      <c r="K191" s="14" t="n"/>
+      <c r="L191" s="14" t="n"/>
+      <c r="M191" s="14" t="n"/>
+    </row>
+    <row r="192">
+      <c r="G192" s="14" t="n"/>
+      <c r="J192" s="14" t="n"/>
+      <c r="K192" s="14" t="n"/>
+      <c r="L192" s="14" t="n"/>
+      <c r="M192" s="14" t="n"/>
+    </row>
+    <row r="193">
+      <c r="G193" s="14" t="n"/>
+      <c r="J193" s="14" t="n"/>
+      <c r="K193" s="14" t="n"/>
+      <c r="L193" s="14" t="n"/>
+      <c r="M193" s="14" t="n"/>
+    </row>
+    <row r="194">
+      <c r="G194" s="14" t="n"/>
+      <c r="J194" s="14" t="n"/>
+      <c r="K194" s="14" t="n"/>
+      <c r="L194" s="14" t="n"/>
+      <c r="M194" s="14" t="n"/>
+    </row>
+    <row r="195">
+      <c r="G195" s="14" t="n"/>
+      <c r="J195" s="14" t="n"/>
+      <c r="K195" s="14" t="n"/>
+      <c r="L195" s="14" t="n"/>
+      <c r="M195" s="14" t="n"/>
+    </row>
+    <row r="196">
+      <c r="G196" s="14" t="n"/>
+      <c r="J196" s="14" t="n"/>
+      <c r="K196" s="14" t="n"/>
+      <c r="L196" s="14" t="n"/>
+      <c r="M196" s="14" t="n"/>
+    </row>
+    <row r="197">
+      <c r="G197" s="14" t="n"/>
+      <c r="J197" s="14" t="n"/>
+      <c r="K197" s="14" t="n"/>
+      <c r="L197" s="14" t="n"/>
+      <c r="M197" s="14" t="n"/>
+    </row>
+    <row r="198">
+      <c r="G198" s="14" t="n"/>
+      <c r="J198" s="14" t="n"/>
+      <c r="K198" s="14" t="n"/>
+      <c r="L198" s="14" t="n"/>
+      <c r="M198" s="14" t="n"/>
+    </row>
+    <row r="199">
+      <c r="G199" s="14" t="n"/>
+      <c r="J199" s="14" t="n"/>
+      <c r="K199" s="14" t="n"/>
+      <c r="L199" s="14" t="n"/>
+      <c r="M199" s="14" t="n"/>
+    </row>
+    <row r="200">
+      <c r="G200" s="14" t="n"/>
+      <c r="J200" s="14" t="n"/>
+      <c r="K200" s="14" t="n"/>
+      <c r="L200" s="14" t="n"/>
+      <c r="M200" s="14" t="n"/>
+    </row>
+    <row r="201">
+      <c r="G201" s="14" t="n"/>
+      <c r="J201" s="14" t="n"/>
+      <c r="K201" s="14" t="n"/>
+      <c r="L201" s="14" t="n"/>
+      <c r="M201" s="14" t="n"/>
+    </row>
+    <row r="202">
+      <c r="G202" s="14" t="n"/>
+      <c r="J202" s="14" t="n"/>
+      <c r="K202" s="14" t="n"/>
+      <c r="L202" s="14" t="n"/>
+      <c r="M202" s="14" t="n"/>
+    </row>
+    <row r="203">
+      <c r="G203" s="14" t="n"/>
+      <c r="J203" s="14" t="n"/>
+      <c r="K203" s="14" t="n"/>
+      <c r="L203" s="14" t="n"/>
+      <c r="M203" s="14" t="n"/>
+    </row>
+    <row r="204">
+      <c r="G204" s="14" t="n"/>
+      <c r="J204" s="14" t="n"/>
+      <c r="K204" s="14" t="n"/>
+      <c r="L204" s="14" t="n"/>
+      <c r="M204" s="14" t="n"/>
+    </row>
+    <row r="205">
+      <c r="G205" s="14" t="n"/>
+      <c r="J205" s="14" t="n"/>
+      <c r="K205" s="14" t="n"/>
+      <c r="L205" s="14" t="n"/>
+      <c r="M205" s="14" t="n"/>
+    </row>
+    <row r="206">
+      <c r="G206" s="14" t="n"/>
+      <c r="J206" s="14" t="n"/>
+      <c r="K206" s="14" t="n"/>
+      <c r="L206" s="14" t="n"/>
+      <c r="M206" s="14" t="n"/>
+    </row>
+    <row r="207">
+      <c r="G207" s="14" t="n"/>
+      <c r="J207" s="14" t="n"/>
+      <c r="K207" s="14" t="n"/>
+      <c r="L207" s="14" t="n"/>
+      <c r="M207" s="14" t="n"/>
+    </row>
+    <row r="208">
+      <c r="G208" s="14" t="n"/>
+      <c r="J208" s="14" t="n"/>
+      <c r="K208" s="14" t="n"/>
+      <c r="L208" s="14" t="n"/>
+      <c r="M208" s="14" t="n"/>
+    </row>
+    <row r="209">
+      <c r="G209" s="14" t="n"/>
+      <c r="J209" s="14" t="n"/>
+      <c r="K209" s="14" t="n"/>
+      <c r="L209" s="14" t="n"/>
+      <c r="M209" s="14" t="n"/>
+    </row>
+    <row r="210">
+      <c r="G210" s="14" t="n"/>
+      <c r="J210" s="14" t="n"/>
+      <c r="K210" s="14" t="n"/>
+      <c r="L210" s="14" t="n"/>
+      <c r="M210" s="14" t="n"/>
+    </row>
+    <row r="211">
+      <c r="G211" s="14" t="n"/>
+      <c r="J211" s="14" t="n"/>
+      <c r="K211" s="14" t="n"/>
+      <c r="L211" s="14" t="n"/>
+      <c r="M211" s="14" t="n"/>
+    </row>
+    <row r="212">
+      <c r="G212" s="14" t="n"/>
+      <c r="J212" s="14" t="n"/>
+      <c r="K212" s="14" t="n"/>
+      <c r="L212" s="14" t="n"/>
+      <c r="M212" s="14" t="n"/>
+    </row>
+    <row r="213">
+      <c r="G213" s="14" t="n"/>
+      <c r="J213" s="14" t="n"/>
+      <c r="K213" s="14" t="n"/>
+      <c r="L213" s="14" t="n"/>
+      <c r="M213" s="14" t="n"/>
+    </row>
+    <row r="214">
+      <c r="G214" s="14" t="n"/>
+      <c r="J214" s="14" t="n"/>
+      <c r="K214" s="14" t="n"/>
+      <c r="L214" s="14" t="n"/>
+      <c r="M214" s="14" t="n"/>
+    </row>
+    <row r="215">
+      <c r="G215" s="14" t="n"/>
+      <c r="J215" s="14" t="n"/>
+      <c r="K215" s="14" t="n"/>
+      <c r="L215" s="14" t="n"/>
+      <c r="M215" s="14" t="n"/>
+    </row>
+    <row r="216">
+      <c r="G216" s="14" t="n"/>
+      <c r="J216" s="14" t="n"/>
+      <c r="K216" s="14" t="n"/>
+      <c r="L216" s="14" t="n"/>
+      <c r="M216" s="14" t="n"/>
+    </row>
+    <row r="217">
+      <c r="G217" s="14" t="n"/>
+      <c r="J217" s="14" t="n"/>
+      <c r="K217" s="14" t="n"/>
+      <c r="L217" s="14" t="n"/>
+      <c r="M217" s="14" t="n"/>
+    </row>
+    <row r="218">
+      <c r="G218" s="14" t="n"/>
+      <c r="J218" s="14" t="n"/>
+      <c r="K218" s="14" t="n"/>
+      <c r="L218" s="14" t="n"/>
+      <c r="M218" s="14" t="n"/>
+    </row>
+    <row r="219">
+      <c r="G219" s="14" t="n"/>
+      <c r="J219" s="14" t="n"/>
+      <c r="K219" s="14" t="n"/>
+      <c r="L219" s="14" t="n"/>
+      <c r="M219" s="14" t="n"/>
+    </row>
+    <row r="220">
+      <c r="G220" s="14" t="n"/>
+      <c r="J220" s="14" t="n"/>
+      <c r="K220" s="14" t="n"/>
+      <c r="L220" s="14" t="n"/>
+      <c r="M220" s="14" t="n"/>
+    </row>
+    <row r="221">
+      <c r="G221" s="14" t="n"/>
+      <c r="J221" s="14" t="n"/>
+      <c r="K221" s="14" t="n"/>
+      <c r="L221" s="14" t="n"/>
+      <c r="M221" s="14" t="n"/>
+    </row>
+    <row r="222">
+      <c r="G222" s="14" t="n"/>
+      <c r="J222" s="14" t="n"/>
+      <c r="K222" s="14" t="n"/>
+      <c r="L222" s="14" t="n"/>
+      <c r="M222" s="14" t="n"/>
+    </row>
+    <row r="223">
+      <c r="G223" s="14" t="n"/>
+      <c r="J223" s="14" t="n"/>
+      <c r="K223" s="14" t="n"/>
+      <c r="L223" s="14" t="n"/>
+      <c r="M223" s="14" t="n"/>
+    </row>
+    <row r="224">
+      <c r="G224" s="14" t="n"/>
+      <c r="J224" s="14" t="n"/>
+      <c r="K224" s="14" t="n"/>
+      <c r="L224" s="14" t="n"/>
+      <c r="M224" s="14" t="n"/>
+    </row>
+    <row r="225">
+      <c r="G225" s="14" t="n"/>
+      <c r="J225" s="14" t="n"/>
+      <c r="K225" s="14" t="n"/>
+      <c r="L225" s="14" t="n"/>
+      <c r="M225" s="14" t="n"/>
+    </row>
+    <row r="226">
+      <c r="G226" s="14" t="n"/>
+      <c r="J226" s="14" t="n"/>
+      <c r="K226" s="14" t="n"/>
+      <c r="L226" s="14" t="n"/>
+      <c r="M226" s="14" t="n"/>
+    </row>
+    <row r="227">
+      <c r="G227" s="14" t="n"/>
+      <c r="J227" s="14" t="n"/>
+      <c r="K227" s="14" t="n"/>
+      <c r="L227" s="14" t="n"/>
+      <c r="M227" s="14" t="n"/>
+    </row>
+    <row r="228">
+      <c r="G228" s="14" t="n"/>
+      <c r="J228" s="14" t="n"/>
+      <c r="K228" s="14" t="n"/>
+      <c r="L228" s="14" t="n"/>
+      <c r="M228" s="14" t="n"/>
+    </row>
+    <row r="229">
+      <c r="G229" s="14" t="n"/>
+      <c r="J229" s="14" t="n"/>
+      <c r="K229" s="14" t="n"/>
+      <c r="L229" s="14" t="n"/>
+      <c r="M229" s="14" t="n"/>
+    </row>
+    <row r="230">
+      <c r="G230" s="14" t="n"/>
+      <c r="J230" s="14" t="n"/>
+      <c r="K230" s="14" t="n"/>
+      <c r="L230" s="14" t="n"/>
+      <c r="M230" s="14" t="n"/>
+    </row>
+    <row r="231">
+      <c r="G231" s="14" t="n"/>
+      <c r="J231" s="14" t="n"/>
+      <c r="K231" s="14" t="n"/>
+      <c r="L231" s="14" t="n"/>
+      <c r="M231" s="14" t="n"/>
+    </row>
+    <row r="232">
+      <c r="G232" s="14" t="n"/>
+      <c r="J232" s="14" t="n"/>
+      <c r="K232" s="14" t="n"/>
+      <c r="L232" s="14" t="n"/>
+      <c r="M232" s="14" t="n"/>
+    </row>
+    <row r="233">
+      <c r="G233" s="14" t="n"/>
+      <c r="J233" s="14" t="n"/>
+      <c r="K233" s="14" t="n"/>
+      <c r="L233" s="14" t="n"/>
+      <c r="M233" s="14" t="n"/>
+    </row>
+    <row r="234">
+      <c r="G234" s="14" t="n"/>
+      <c r="J234" s="14" t="n"/>
+      <c r="K234" s="14" t="n"/>
+      <c r="L234" s="14" t="n"/>
+      <c r="M234" s="14" t="n"/>
+    </row>
+    <row r="235">
+      <c r="G235" s="14" t="n"/>
+      <c r="J235" s="14" t="n"/>
+      <c r="K235" s="14" t="n"/>
+      <c r="L235" s="14" t="n"/>
+      <c r="M235" s="14" t="n"/>
+    </row>
+    <row r="236">
+      <c r="G236" s="14" t="n"/>
+      <c r="J236" s="14" t="n"/>
+      <c r="K236" s="14" t="n"/>
+      <c r="L236" s="14" t="n"/>
+      <c r="M236" s="14" t="n"/>
+    </row>
+    <row r="237">
+      <c r="G237" s="14" t="n"/>
+      <c r="J237" s="14" t="n"/>
+      <c r="K237" s="14" t="n"/>
+      <c r="L237" s="14" t="n"/>
+      <c r="M237" s="14" t="n"/>
+    </row>
+    <row r="238">
+      <c r="G238" s="14" t="n"/>
+      <c r="J238" s="14" t="n"/>
+      <c r="K238" s="14" t="n"/>
+      <c r="L238" s="14" t="n"/>
+      <c r="M238" s="14" t="n"/>
+    </row>
+    <row r="239">
+      <c r="G239" s="14" t="n"/>
+      <c r="J239" s="14" t="n"/>
+      <c r="K239" s="14" t="n"/>
+      <c r="L239" s="14" t="n"/>
+      <c r="M239" s="14" t="n"/>
+    </row>
+    <row r="240">
+      <c r="G240" s="14" t="n"/>
+      <c r="J240" s="14" t="n"/>
+      <c r="K240" s="14" t="n"/>
+      <c r="L240" s="14" t="n"/>
+      <c r="M240" s="14" t="n"/>
+    </row>
+    <row r="241">
+      <c r="G241" s="14" t="n"/>
+      <c r="J241" s="14" t="n"/>
+      <c r="K241" s="14" t="n"/>
+      <c r="L241" s="14" t="n"/>
+      <c r="M241" s="14" t="n"/>
+    </row>
+    <row r="242">
+      <c r="G242" s="14" t="n"/>
+      <c r="J242" s="14" t="n"/>
+      <c r="K242" s="14" t="n"/>
+      <c r="L242" s="14" t="n"/>
+      <c r="M242" s="14" t="n"/>
+    </row>
+    <row r="243">
+      <c r="G243" s="14" t="n"/>
+      <c r="J243" s="14" t="n"/>
+      <c r="K243" s="14" t="n"/>
+      <c r="L243" s="14" t="n"/>
+      <c r="M243" s="14" t="n"/>
+    </row>
+    <row r="244">
+      <c r="G244" s="14" t="n"/>
+      <c r="J244" s="14" t="n"/>
+      <c r="K244" s="14" t="n"/>
+      <c r="L244" s="14" t="n"/>
+      <c r="M244" s="14" t="n"/>
+    </row>
+    <row r="245">
+      <c r="G245" s="14" t="n"/>
+      <c r="J245" s="14" t="n"/>
+      <c r="K245" s="14" t="n"/>
+      <c r="L245" s="14" t="n"/>
+      <c r="M245" s="14" t="n"/>
+    </row>
+    <row r="246">
+      <c r="G246" s="14" t="n"/>
+      <c r="J246" s="14" t="n"/>
+      <c r="K246" s="14" t="n"/>
+      <c r="L246" s="14" t="n"/>
+      <c r="M246" s="14" t="n"/>
+    </row>
+    <row r="247">
+      <c r="G247" s="14" t="n"/>
+      <c r="J247" s="14" t="n"/>
+      <c r="K247" s="14" t="n"/>
+      <c r="L247" s="14" t="n"/>
+      <c r="M247" s="14" t="n"/>
+    </row>
+    <row r="248">
+      <c r="G248" s="14" t="n"/>
+      <c r="J248" s="14" t="n"/>
+      <c r="K248" s="14" t="n"/>
+      <c r="L248" s="14" t="n"/>
+      <c r="M248" s="14" t="n"/>
+    </row>
+    <row r="249">
+      <c r="G249" s="14" t="n"/>
+      <c r="J249" s="14" t="n"/>
+      <c r="K249" s="14" t="n"/>
+      <c r="L249" s="14" t="n"/>
+      <c r="M249" s="14" t="n"/>
+    </row>
+    <row r="250">
+      <c r="G250" s="14" t="n"/>
+      <c r="J250" s="14" t="n"/>
+      <c r="K250" s="14" t="n"/>
+      <c r="L250" s="14" t="n"/>
+      <c r="M250" s="14" t="n"/>
+    </row>
+    <row r="251">
+      <c r="G251" s="14" t="n"/>
+      <c r="J251" s="14" t="n"/>
+      <c r="K251" s="14" t="n"/>
+      <c r="L251" s="14" t="n"/>
+      <c r="M251" s="14" t="n"/>
+    </row>
+    <row r="252">
+      <c r="G252" s="14" t="n"/>
+      <c r="J252" s="14" t="n"/>
+      <c r="K252" s="14" t="n"/>
+      <c r="L252" s="14" t="n"/>
+      <c r="M252" s="14" t="n"/>
+    </row>
+    <row r="253">
+      <c r="G253" s="14" t="n"/>
+      <c r="J253" s="14" t="n"/>
+      <c r="K253" s="14" t="n"/>
+      <c r="L253" s="14" t="n"/>
+      <c r="M253" s="14" t="n"/>
+    </row>
+    <row r="254">
+      <c r="G254" s="14" t="n"/>
+      <c r="J254" s="14" t="n"/>
+      <c r="K254" s="14" t="n"/>
+      <c r="L254" s="14" t="n"/>
+      <c r="M254" s="14" t="n"/>
+    </row>
+    <row r="255">
+      <c r="G255" s="14" t="n"/>
+      <c r="J255" s="14" t="n"/>
+      <c r="K255" s="14" t="n"/>
+      <c r="L255" s="14" t="n"/>
+      <c r="M255" s="14" t="n"/>
+    </row>
+    <row r="256">
+      <c r="G256" s="14" t="n"/>
+      <c r="J256" s="14" t="n"/>
+      <c r="K256" s="14" t="n"/>
+      <c r="L256" s="14" t="n"/>
+      <c r="M256" s="14" t="n"/>
+    </row>
+    <row r="257">
+      <c r="G257" s="14" t="n"/>
+      <c r="J257" s="14" t="n"/>
+      <c r="K257" s="14" t="n"/>
+      <c r="L257" s="14" t="n"/>
+      <c r="M257" s="14" t="n"/>
+    </row>
+    <row r="258">
+      <c r="G258" s="14" t="n"/>
+      <c r="J258" s="14" t="n"/>
+      <c r="K258" s="14" t="n"/>
+      <c r="L258" s="14" t="n"/>
+      <c r="M258" s="14" t="n"/>
+    </row>
+    <row r="259">
+      <c r="G259" s="14" t="n"/>
+      <c r="J259" s="14" t="n"/>
+      <c r="K259" s="14" t="n"/>
+      <c r="L259" s="14" t="n"/>
+      <c r="M259" s="14" t="n"/>
+    </row>
+    <row r="260">
+      <c r="G260" s="14" t="n"/>
+      <c r="J260" s="14" t="n"/>
+      <c r="K260" s="14" t="n"/>
+      <c r="L260" s="14" t="n"/>
+      <c r="M260" s="14" t="n"/>
+    </row>
+    <row r="261">
+      <c r="G261" s="14" t="n"/>
+      <c r="J261" s="14" t="n"/>
+      <c r="K261" s="14" t="n"/>
+      <c r="L261" s="14" t="n"/>
+      <c r="M261" s="14" t="n"/>
+    </row>
+    <row r="262">
+      <c r="G262" s="14" t="n"/>
+      <c r="J262" s="14" t="n"/>
+      <c r="K262" s="14" t="n"/>
+      <c r="L262" s="14" t="n"/>
+      <c r="M262" s="14" t="n"/>
+    </row>
+    <row r="263">
+      <c r="G263" s="14" t="n"/>
+      <c r="J263" s="14" t="n"/>
+      <c r="K263" s="14" t="n"/>
+      <c r="L263" s="14" t="n"/>
+      <c r="M263" s="14" t="n"/>
+    </row>
+    <row r="264">
+      <c r="G264" s="14" t="n"/>
+      <c r="J264" s="14" t="n"/>
+      <c r="K264" s="14" t="n"/>
+      <c r="L264" s="14" t="n"/>
+      <c r="M264" s="14" t="n"/>
+    </row>
+    <row r="265">
+      <c r="G265" s="14" t="n"/>
+      <c r="J265" s="14" t="n"/>
+      <c r="K265" s="14" t="n"/>
+      <c r="L265" s="14" t="n"/>
+      <c r="M265" s="14" t="n"/>
+    </row>
+    <row r="266">
+      <c r="G266" s="14" t="n"/>
+      <c r="J266" s="14" t="n"/>
+      <c r="K266" s="14" t="n"/>
+      <c r="L266" s="14" t="n"/>
+      <c r="M266" s="14" t="n"/>
+    </row>
+    <row r="267">
+      <c r="G267" s="14" t="n"/>
+      <c r="J267" s="14" t="n"/>
+      <c r="K267" s="14" t="n"/>
+      <c r="L267" s="14" t="n"/>
+      <c r="M267" s="14" t="n"/>
+    </row>
+    <row r="268">
+      <c r="G268" s="14" t="n"/>
+      <c r="J268" s="14" t="n"/>
+      <c r="K268" s="14" t="n"/>
+      <c r="L268" s="14" t="n"/>
+      <c r="M268" s="14" t="n"/>
+    </row>
+    <row r="269">
+      <c r="G269" s="14" t="n"/>
+      <c r="J269" s="14" t="n"/>
+      <c r="K269" s="14" t="n"/>
+      <c r="L269" s="14" t="n"/>
+      <c r="M269" s="14" t="n"/>
+    </row>
+    <row r="270">
+      <c r="G270" s="14" t="n"/>
+      <c r="J270" s="14" t="n"/>
+      <c r="K270" s="14" t="n"/>
+      <c r="L270" s="14" t="n"/>
+      <c r="M270" s="14" t="n"/>
+    </row>
+    <row r="271">
+      <c r="G271" s="14" t="n"/>
+      <c r="J271" s="14" t="n"/>
+      <c r="K271" s="14" t="n"/>
+      <c r="L271" s="14" t="n"/>
+      <c r="M271" s="14" t="n"/>
+    </row>
+    <row r="272">
+      <c r="G272" s="14" t="n"/>
+      <c r="J272" s="14" t="n"/>
+      <c r="K272" s="14" t="n"/>
+      <c r="L272" s="14" t="n"/>
+      <c r="M272" s="14" t="n"/>
+    </row>
+    <row r="273">
+      <c r="G273" s="14" t="n"/>
+      <c r="J273" s="14" t="n"/>
+      <c r="K273" s="14" t="n"/>
+      <c r="L273" s="14" t="n"/>
+      <c r="M273" s="14" t="n"/>
+    </row>
+    <row r="274">
+      <c r="G274" s="14" t="n"/>
+      <c r="J274" s="14" t="n"/>
+      <c r="K274" s="14" t="n"/>
+      <c r="L274" s="14" t="n"/>
+      <c r="M274" s="14" t="n"/>
+    </row>
+    <row r="275">
+      <c r="G275" s="14" t="n"/>
+      <c r="J275" s="14" t="n"/>
+      <c r="K275" s="14" t="n"/>
+      <c r="L275" s="14" t="n"/>
+      <c r="M275" s="14" t="n"/>
+    </row>
+    <row r="276">
+      <c r="G276" s="14" t="n"/>
+      <c r="J276" s="14" t="n"/>
+      <c r="K276" s="14" t="n"/>
+      <c r="L276" s="14" t="n"/>
+      <c r="M276" s="14" t="n"/>
+    </row>
+    <row r="277">
+      <c r="G277" s="14" t="n"/>
+      <c r="J277" s="14" t="n"/>
+      <c r="K277" s="14" t="n"/>
+      <c r="L277" s="14" t="n"/>
+      <c r="M277" s="14" t="n"/>
+    </row>
+    <row r="278">
+      <c r="G278" s="14" t="n"/>
+      <c r="J278" s="14" t="n"/>
+      <c r="K278" s="14" t="n"/>
+      <c r="L278" s="14" t="n"/>
+      <c r="M278" s="14" t="n"/>
+    </row>
+    <row r="279">
+      <c r="G279" s="14" t="n"/>
+      <c r="J279" s="14" t="n"/>
+      <c r="K279" s="14" t="n"/>
+      <c r="L279" s="14" t="n"/>
+      <c r="M279" s="14" t="n"/>
+    </row>
+    <row r="280">
+      <c r="G280" s="14" t="n"/>
+      <c r="J280" s="14" t="n"/>
+      <c r="K280" s="14" t="n"/>
+      <c r="L280" s="14" t="n"/>
+      <c r="M280" s="14" t="n"/>
+    </row>
+    <row r="281">
+      <c r="G281" s="14" t="n"/>
+      <c r="J281" s="14" t="n"/>
+      <c r="K281" s="14" t="n"/>
+      <c r="L281" s="14" t="n"/>
+      <c r="M281" s="14" t="n"/>
+    </row>
+    <row r="282">
+      <c r="G282" s="14" t="n"/>
+      <c r="J282" s="14" t="n"/>
+      <c r="K282" s="14" t="n"/>
+      <c r="L282" s="14" t="n"/>
+      <c r="M282" s="14" t="n"/>
+    </row>
+    <row r="283">
+      <c r="G283" s="14" t="n"/>
+      <c r="J283" s="14" t="n"/>
+      <c r="K283" s="14" t="n"/>
+      <c r="L283" s="14" t="n"/>
+      <c r="M283" s="14" t="n"/>
+    </row>
+    <row r="284">
+      <c r="G284" s="14" t="n"/>
+      <c r="J284" s="14" t="n"/>
+      <c r="K284" s="14" t="n"/>
+      <c r="L284" s="14" t="n"/>
+      <c r="M284" s="14" t="n"/>
+    </row>
+    <row r="285">
+      <c r="G285" s="14" t="n"/>
+      <c r="J285" s="14" t="n"/>
+      <c r="K285" s="14" t="n"/>
+      <c r="L285" s="14" t="n"/>
+      <c r="M285" s="14" t="n"/>
+    </row>
+    <row r="286">
+      <c r="G286" s="14" t="n"/>
+      <c r="J286" s="14" t="n"/>
+      <c r="K286" s="14" t="n"/>
+      <c r="L286" s="14" t="n"/>
+      <c r="M286" s="14" t="n"/>
+    </row>
+    <row r="287">
+      <c r="G287" s="14" t="n"/>
+      <c r="J287" s="14" t="n"/>
+      <c r="K287" s="14" t="n"/>
+      <c r="L287" s="14" t="n"/>
+      <c r="M287" s="14" t="n"/>
+    </row>
+    <row r="288">
+      <c r="G288" s="14" t="n"/>
+      <c r="J288" s="14" t="n"/>
+      <c r="K288" s="14" t="n"/>
+      <c r="L288" s="14" t="n"/>
+      <c r="M288" s="14" t="n"/>
+    </row>
+    <row r="289">
+      <c r="G289" s="14" t="n"/>
+      <c r="J289" s="14" t="n"/>
+      <c r="K289" s="14" t="n"/>
+      <c r="L289" s="14" t="n"/>
+      <c r="M289" s="14" t="n"/>
+    </row>
+    <row r="290">
+      <c r="G290" s="14" t="n"/>
+      <c r="J290" s="14" t="n"/>
+      <c r="K290" s="14" t="n"/>
+      <c r="L290" s="14" t="n"/>
+      <c r="M290" s="14" t="n"/>
+    </row>
+    <row r="291">
+      <c r="G291" s="14" t="n"/>
+      <c r="J291" s="14" t="n"/>
+      <c r="K291" s="14" t="n"/>
+      <c r="L291" s="14" t="n"/>
+      <c r="M291" s="14" t="n"/>
+    </row>
+    <row r="292">
+      <c r="G292" s="14" t="n"/>
+      <c r="J292" s="14" t="n"/>
+      <c r="K292" s="14" t="n"/>
+      <c r="L292" s="14" t="n"/>
+      <c r="M292" s="14" t="n"/>
+    </row>
+    <row r="293">
+      <c r="G293" s="14" t="n"/>
+      <c r="J293" s="14" t="n"/>
+      <c r="K293" s="14" t="n"/>
+      <c r="L293" s="14" t="n"/>
+      <c r="M293" s="14" t="n"/>
+    </row>
+    <row r="294">
+      <c r="G294" s="14" t="n"/>
+      <c r="J294" s="14" t="n"/>
+      <c r="K294" s="14" t="n"/>
+      <c r="L294" s="14" t="n"/>
+      <c r="M294" s="14" t="n"/>
+    </row>
+    <row r="295">
+      <c r="G295" s="14" t="n"/>
+      <c r="J295" s="14" t="n"/>
+      <c r="K295" s="14" t="n"/>
+      <c r="L295" s="14" t="n"/>
+      <c r="M295" s="14" t="n"/>
+    </row>
+    <row r="296">
+      <c r="G296" s="14" t="n"/>
+      <c r="J296" s="14" t="n"/>
+      <c r="K296" s="14" t="n"/>
+      <c r="L296" s="14" t="n"/>
+      <c r="M296" s="14" t="n"/>
+    </row>
+    <row r="297">
+      <c r="G297" s="14" t="n"/>
+      <c r="J297" s="14" t="n"/>
+      <c r="K297" s="14" t="n"/>
+      <c r="L297" s="14" t="n"/>
+      <c r="M297" s="14" t="n"/>
+    </row>
+    <row r="298">
+      <c r="G298" s="14" t="n"/>
+      <c r="J298" s="14" t="n"/>
+      <c r="K298" s="14" t="n"/>
+      <c r="L298" s="14" t="n"/>
+      <c r="M298" s="14" t="n"/>
+    </row>
+    <row r="299">
+      <c r="G299" s="14" t="n"/>
+      <c r="J299" s="14" t="n"/>
+      <c r="K299" s="14" t="n"/>
+      <c r="L299" s="14" t="n"/>
+      <c r="M299" s="14" t="n"/>
+    </row>
+    <row r="300">
+      <c r="G300" s="14" t="n"/>
+      <c r="J300" s="14" t="n"/>
+      <c r="K300" s="14" t="n"/>
+      <c r="L300" s="14" t="n"/>
+      <c r="M300" s="14" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">
